--- a/週報模板.xlsx
+++ b/週報模板.xlsx
@@ -421,7 +421,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -755,6 +755,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -4642,28 +4648,28 @@
           <t>人均產值</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n"/>
-      <c r="C31" s="37" t="n"/>
-      <c r="D31" s="38" t="n">
+      <c r="B31" s="115" t="n"/>
+      <c r="C31" s="115" t="n"/>
+      <c r="D31" s="116" t="n">
         <v>100000</v>
       </c>
       <c r="E31" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="F31" s="37" t="n"/>
+      <c r="F31" s="115" t="n"/>
       <c r="G31" s="32" t="n"/>
       <c r="H31" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="37" t="n"/>
-      <c r="J31" s="38" t="n">
+      <c r="I31" s="115" t="n"/>
+      <c r="J31" s="116" t="n">
         <v>-800000</v>
       </c>
       <c r="K31" s="31" t="n">
         <v>-0.32</v>
       </c>
-      <c r="L31" s="37" t="n"/>
-      <c r="M31" s="38" t="n">
+      <c r="L31" s="115" t="n"/>
+      <c r="M31" s="116" t="n">
         <v>300000</v>
       </c>
       <c r="N31" s="31" t="n">
@@ -4676,15 +4682,15 @@
           <t>來客數</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n"/>
-      <c r="C32" s="37" t="n"/>
-      <c r="D32" s="38" t="n">
+      <c r="B32" s="115" t="n"/>
+      <c r="C32" s="115" t="n"/>
+      <c r="D32" s="116" t="n">
         <v>-200</v>
       </c>
       <c r="E32" s="31" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F32" s="37" t="n"/>
+      <c r="F32" s="115" t="n"/>
       <c r="G32" s="30" t="n">
         <v>0</v>
       </c>
@@ -4692,14 +4698,14 @@
         <v>0</v>
       </c>
       <c r="I32" s="29" t="n"/>
-      <c r="J32" s="38" t="n">
+      <c r="J32" s="116" t="n">
         <v>-500</v>
       </c>
       <c r="K32" s="31" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L32" s="37" t="n"/>
-      <c r="M32" s="38" t="n">
+      <c r="L32" s="115" t="n"/>
+      <c r="M32" s="116" t="n">
         <v>-900</v>
       </c>
       <c r="N32" s="31" t="n">

--- a/週報模板.xlsx
+++ b/週報模板.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="680" windowWidth="28240" windowHeight="16740" tabRatio="600" firstSheet="3" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="680" windowWidth="28240" windowHeight="16740" tabRatio="600" firstSheet="3" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.主機銷售台數" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.門市週報 " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.3PP配件比較" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.3PP 銷售排名" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.VAP銷售排名" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.搭售統計_週" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.搭售統計_月" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.個人新制獎金" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.個人週主機" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.個人月主機" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.個人月3PP" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.月報YOY" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.3PP YOY" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="設定" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1.主機銷售台數" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2.門市週報 " sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3.每月重點" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4.Speakers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5.3PP配件比較" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6.3PP 銷售排名" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7.VAP銷售排名" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8.搭售統計_週" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9.搭售統計_月" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10.個人新制獎金" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11.個人週主機" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12.個人月主機" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13.個人月3PP" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14.月報YOY" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15.3PP YOY" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34,7 +36,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="新細明體"/>
       <charset val="136"/>
@@ -209,8 +211,24 @@
       <color rgb="00EF4335"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="0"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -390,6 +408,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D7D9DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -673,7 +703,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1129,6 +1159,37 @@
     </xf>
     <xf numFmtId="9" fontId="25" fillId="31" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1660,6 +1721,1400 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AA12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" style="106" min="1" max="1"/>
+    <col width="10.5" customWidth="1" style="106" min="2" max="2"/>
+    <col width="10.5" customWidth="1" style="106" min="3" max="3"/>
+    <col width="10.5" customWidth="1" style="106" min="4" max="4"/>
+    <col width="10.5" customWidth="1" style="106" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="106" min="6" max="6"/>
+    <col width="10.5" customWidth="1" style="106" min="7" max="7"/>
+    <col width="10.5" customWidth="1" style="106" min="8" max="8"/>
+    <col width="10.5" customWidth="1" style="106" min="9" max="9"/>
+    <col width="10.5" customWidth="1" style="106" min="10" max="10"/>
+    <col width="10.5" customWidth="1" style="106" min="11" max="11"/>
+    <col width="10.5" customWidth="1" style="106" min="12" max="12"/>
+    <col width="10.5" customWidth="1" style="106" min="13" max="13"/>
+    <col width="10.5" customWidth="1" style="106" min="14" max="14"/>
+    <col width="10.5" customWidth="1" style="106" min="15" max="15"/>
+    <col width="10.5" customWidth="1" style="106" min="16" max="16"/>
+    <col width="10.5" customWidth="1" style="106" min="17" max="17"/>
+    <col width="10.5" customWidth="1" style="106" min="18" max="18"/>
+    <col width="10.5" customWidth="1" style="106" min="19" max="19"/>
+    <col width="10.5" customWidth="1" style="106" min="20" max="20"/>
+    <col width="10.5" customWidth="1" style="106" min="21" max="21"/>
+    <col width="10.5" customWidth="1" style="106" min="22" max="22"/>
+    <col width="10.5" customWidth="1" style="106" min="23" max="23"/>
+    <col width="10.5" customWidth="1" style="106" min="24" max="24"/>
+    <col width="10.5" customWidth="1" style="106" min="25" max="25"/>
+    <col width="10.5" customWidth="1" style="106" min="26" max="26"/>
+    <col width="10.5" customWidth="1" style="106" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" s="106">
+      <c r="A1" s="116" t="inlineStr">
+        <is>
+          <t>士林</t>
+        </is>
+      </c>
+      <c r="B1" s="117" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C1" s="117" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="D1" s="117" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="E1" s="117" t="inlineStr">
+        <is>
+          <t>CPU
+零搭售</t>
+        </is>
+      </c>
+      <c r="F1" s="118" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="G1" s="119" t="inlineStr">
+        <is>
+          <t>iPhone</t>
+        </is>
+      </c>
+      <c r="H1" s="119" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="I1" s="119" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="J1" s="119" t="inlineStr">
+        <is>
+          <t>iPhone
+零搭售</t>
+        </is>
+      </c>
+      <c r="K1" s="120" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="L1" s="121" t="inlineStr">
+        <is>
+          <t>iPad</t>
+        </is>
+      </c>
+      <c r="M1" s="121" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="N1" s="121" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="O1" s="121" t="inlineStr">
+        <is>
+          <t>iPad
+零搭售</t>
+        </is>
+      </c>
+      <c r="P1" s="122" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="Q1" s="123" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="R1" s="123" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="S1" s="123" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="T1" s="123" t="inlineStr">
+        <is>
+          <t>Watch
+零搭售</t>
+        </is>
+      </c>
+      <c r="U1" s="124" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="V1" s="125" t="inlineStr">
+        <is>
+          <t>AirPods</t>
+        </is>
+      </c>
+      <c r="W1" s="125" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="X1" s="125" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="Y1" s="125" t="inlineStr">
+        <is>
+          <t>AirPods
+零搭售</t>
+        </is>
+      </c>
+      <c r="Z1" s="126" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="AA1" s="127" t="inlineStr">
+        <is>
+          <t>3PP
+搭售率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1" s="106">
+      <c r="A2" s="128" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="B2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="130" t="n"/>
+      <c r="E2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="131" t="n"/>
+      <c r="G2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="130" t="n"/>
+      <c r="J2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="131" t="n"/>
+      <c r="L2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="130" t="n"/>
+      <c r="O2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="131" t="n"/>
+      <c r="Q2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="130" t="n"/>
+      <c r="T2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="131" t="n"/>
+      <c r="V2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="130" t="n"/>
+      <c r="Y2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="131" t="n"/>
+      <c r="AA2" s="132" t="n"/>
+    </row>
+    <row r="3" ht="38" customHeight="1" s="106">
+      <c r="A3" s="128" t="inlineStr">
+        <is>
+          <t>Dean</t>
+        </is>
+      </c>
+      <c r="B3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="140" t="n"/>
+      <c r="E3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="155" t="n"/>
+      <c r="G3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="133" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="133" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="133" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" s="134" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" s="133" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" s="134" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA3" s="136" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1" s="106">
+      <c r="A4" s="128" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="130" t="n"/>
+      <c r="E4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="131" t="n"/>
+      <c r="G4" s="129" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="129" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" s="137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="130" t="n"/>
+      <c r="O4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="131" t="n"/>
+      <c r="Q4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="130" t="n"/>
+      <c r="T4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="131" t="n"/>
+      <c r="V4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="130" t="n"/>
+      <c r="Y4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="131" t="n"/>
+      <c r="AA4" s="139" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1" s="106">
+      <c r="A5" s="128" t="inlineStr">
+        <is>
+          <t>Nana</t>
+        </is>
+      </c>
+      <c r="B5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="133" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="134" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="133" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" s="134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="140" t="n"/>
+      <c r="T5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" s="135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="133" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="135" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AA5" s="136" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1" s="106">
+      <c r="A6" s="128" t="inlineStr">
+        <is>
+          <t>Zoe</t>
+        </is>
+      </c>
+      <c r="B6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="130" t="n"/>
+      <c r="E6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="131" t="n"/>
+      <c r="G6" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="129" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="138" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="137" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V6" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="137" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="129" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="138" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AA6" s="139" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1" s="106">
+      <c r="A7" s="128" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+      <c r="B7" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="133" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="134" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="133" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="140" t="n"/>
+      <c r="T7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="155" t="n"/>
+      <c r="V7" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="136" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1" s="106">
+      <c r="A8" s="128" t="inlineStr">
+        <is>
+          <t>Tanya</t>
+        </is>
+      </c>
+      <c r="B8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="130" t="n"/>
+      <c r="E8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="131" t="n"/>
+      <c r="G8" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="129" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" s="137" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J8" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="138" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L8" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="129" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="130" t="n"/>
+      <c r="Y8" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="139" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1" s="106">
+      <c r="A9" s="141" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="142" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="142" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="142" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" s="142" t="n">
+        <v>62</v>
+      </c>
+      <c r="I9" s="143" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J9" s="142" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="144" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L9" s="142" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" s="142" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" s="143" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O9" s="142" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="144" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q9" s="142" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" s="142" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" s="143" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T9" s="142" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" s="144" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V9" s="142" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" s="142" t="n">
+        <v>7</v>
+      </c>
+      <c r="X9" s="143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y9" s="142" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" s="144" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA9" s="145" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1" s="106">
+      <c r="A10" s="146" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B10" s="147" t="n">
+        <v>23</v>
+      </c>
+      <c r="C10" s="147" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="148" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E10" s="147" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="149" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G10" s="147" t="n">
+        <v>81</v>
+      </c>
+      <c r="H10" s="147" t="n">
+        <v>295</v>
+      </c>
+      <c r="I10" s="148" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J10" s="147" t="n">
+        <v>45</v>
+      </c>
+      <c r="K10" s="149" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L10" s="147" t="n">
+        <v>51</v>
+      </c>
+      <c r="M10" s="147" t="n">
+        <v>122</v>
+      </c>
+      <c r="N10" s="148" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O10" s="147" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" s="149" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q10" s="147" t="n">
+        <v>37</v>
+      </c>
+      <c r="R10" s="147" t="n">
+        <v>63</v>
+      </c>
+      <c r="S10" s="148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T10" s="147" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" s="149" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V10" s="147" t="n">
+        <v>45</v>
+      </c>
+      <c r="W10" s="147" t="n">
+        <v>86</v>
+      </c>
+      <c r="X10" s="148" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y10" s="147" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z10" s="149" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AA10" s="150" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1" s="106">
+      <c r="A11" s="146" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B11" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="151" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" s="152" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E11" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="151" t="n">
+        <v>62</v>
+      </c>
+      <c r="H11" s="151" t="n">
+        <v>220</v>
+      </c>
+      <c r="I11" s="152" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J11" s="151" t="n">
+        <v>43</v>
+      </c>
+      <c r="K11" s="153" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L11" s="151" t="n">
+        <v>56</v>
+      </c>
+      <c r="M11" s="151" t="n">
+        <v>156</v>
+      </c>
+      <c r="N11" s="152" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O11" s="151" t="n">
+        <v>12</v>
+      </c>
+      <c r="P11" s="153" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q11" s="151" t="n">
+        <v>30</v>
+      </c>
+      <c r="R11" s="151" t="n">
+        <v>51</v>
+      </c>
+      <c r="S11" s="152" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T11" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="U11" s="153" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V11" s="151" t="n">
+        <v>37</v>
+      </c>
+      <c r="W11" s="151" t="n">
+        <v>74</v>
+      </c>
+      <c r="X11" s="152" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z11" s="153" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AA11" s="154" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1" s="106">
+      <c r="A12" s="146" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B12" s="147" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="147" t="n">
+        <v>36</v>
+      </c>
+      <c r="D12" s="148" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="147" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="149" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G12" s="147" t="n">
+        <v>79</v>
+      </c>
+      <c r="H12" s="147" t="n">
+        <v>243</v>
+      </c>
+      <c r="I12" s="148" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J12" s="147" t="n">
+        <v>56</v>
+      </c>
+      <c r="K12" s="149" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L12" s="147" t="n">
+        <v>32</v>
+      </c>
+      <c r="M12" s="147" t="n">
+        <v>87</v>
+      </c>
+      <c r="N12" s="148" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O12" s="147" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" s="149" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Q12" s="147" t="n">
+        <v>29</v>
+      </c>
+      <c r="R12" s="147" t="n">
+        <v>45</v>
+      </c>
+      <c r="S12" s="148" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T12" s="147" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" s="149" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V12" s="147" t="n">
+        <v>48</v>
+      </c>
+      <c r="W12" s="147" t="n">
+        <v>89</v>
+      </c>
+      <c r="X12" s="148" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y12" s="147" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z12" s="149" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AA12" s="150" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="17.6640625" customWidth="1" style="106" min="1" max="1"/>
+    <col width="15.1640625" customWidth="1" style="106" min="2" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="57" customHeight="1" s="106">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="43" t="inlineStr">
+        <is>
+          <t>營業額 +(不含SA Care)</t>
+        </is>
+      </c>
+      <c r="C1" s="43" t="inlineStr">
+        <is>
+          <t>3PP 營業額 +(不含SA Care)</t>
+        </is>
+      </c>
+      <c r="D1" s="43" t="inlineStr">
+        <is>
+          <t>原廠商品 +營業額</t>
+        </is>
+      </c>
+      <c r="E1" s="43" t="inlineStr">
+        <is>
+          <t>SA Care +金額(含稅)</t>
+        </is>
+      </c>
+      <c r="F1" s="43" t="inlineStr">
+        <is>
+          <t>純SA Care +搭售率</t>
+        </is>
+      </c>
+      <c r="G1" s="43" t="inlineStr">
+        <is>
+          <t>純3PP 搭售率</t>
+        </is>
+      </c>
+      <c r="H1" s="44" t="inlineStr">
+        <is>
+          <t>原廠商品 +毛利額</t>
+        </is>
+      </c>
+      <c r="I1" s="44" t="inlineStr">
+        <is>
+          <t>3pp商品 +毛利額</t>
+        </is>
+      </c>
+      <c r="J1" s="44" t="inlineStr">
+        <is>
+          <t>SA Care +毛利額</t>
+        </is>
+      </c>
+      <c r="K1" s="45" t="inlineStr">
+        <is>
+          <t>總毛利額</t>
+        </is>
+      </c>
+      <c r="L1" s="44" t="inlineStr">
+        <is>
+          <t>毛利目標</t>
+        </is>
+      </c>
+      <c r="M1" s="44" t="inlineStr">
+        <is>
+          <t>達成率</t>
+        </is>
+      </c>
+      <c r="N1" s="46" t="inlineStr">
+        <is>
+          <t>累計獎金</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1" s="106">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="115">
+        <f>E2/(E2+B2)</f>
+        <v/>
+      </c>
+      <c r="G2" s="115">
+        <f>C2/B2</f>
+        <v/>
+      </c>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="60">
+        <f>E2/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K2" s="28">
+        <f>H2+I2+J2</f>
+        <v/>
+      </c>
+      <c r="L2" s="28" t="n"/>
+      <c r="M2" s="28" t="n"/>
+      <c r="N2" s="28" t="n"/>
+    </row>
+    <row r="3" ht="52" customHeight="1" s="106">
+      <c r="A3" s="53" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="115">
+        <f>E3/(E3+B3)</f>
+        <v/>
+      </c>
+      <c r="G3" s="115">
+        <f>C3/B3</f>
+        <v/>
+      </c>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="60">
+        <f>E3/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K3" s="28">
+        <f>H3+I3+J3</f>
+        <v/>
+      </c>
+      <c r="L3" s="48" t="n"/>
+      <c r="M3" s="47" t="n"/>
+      <c r="N3" s="48" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1" s="106">
+      <c r="A4" s="53" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="115">
+        <f>E4/(E4+B4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="115">
+        <f>C4/B4</f>
+        <v/>
+      </c>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="60">
+        <f>E4/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K4" s="28">
+        <f>H4+I4+J4</f>
+        <v/>
+      </c>
+      <c r="L4" s="48" t="n"/>
+      <c r="M4" s="47" t="n"/>
+      <c r="N4" s="48" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1" s="106">
+      <c r="A5" s="53" t="n"/>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="115">
+        <f>E5/(E5+B5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="115">
+        <f>C5/B5</f>
+        <v/>
+      </c>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="60">
+        <f>E5/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K5" s="28">
+        <f>H5+I5+J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="48" t="n"/>
+      <c r="M5" s="47" t="n"/>
+      <c r="N5" s="48" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1" s="106">
+      <c r="A6" s="53" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="115">
+        <f>E6/(E6+B6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="115">
+        <f>C6/B6</f>
+        <v/>
+      </c>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="60">
+        <f>E6/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K6" s="28">
+        <f>H6+I6+J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="48" t="n"/>
+      <c r="M6" s="47" t="n"/>
+      <c r="N6" s="48" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1" s="106">
+      <c r="A7" s="53" t="n"/>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="115">
+        <f>E7/(E7+B7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="115">
+        <f>C7/B7</f>
+        <v/>
+      </c>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="60">
+        <f>E7/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K7" s="28">
+        <f>H7+I7+J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="48" t="n"/>
+      <c r="M7" s="47" t="n"/>
+      <c r="N7" s="48" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1" s="106">
+      <c r="A8" s="53" t="n"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="115">
+        <f>E8/(E8+B8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="115">
+        <f>C8/B8</f>
+        <v/>
+      </c>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="60">
+        <f>E8/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K8" s="28">
+        <f>H8+I8+J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="48" t="n"/>
+      <c r="M8" s="47" t="n"/>
+      <c r="N8" s="48" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1" s="106">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>加總</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="115">
+        <f>E9/(E9+B9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="115">
+        <f>C9/B9</f>
+        <v/>
+      </c>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="60">
+        <f>E9/2/1.05</f>
+        <v/>
+      </c>
+      <c r="K9" s="28">
+        <f>H9+I9+J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="48" t="n"/>
+      <c r="M9" s="47" t="n"/>
+      <c r="N9" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -1984,7 +3439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2314,7 +3769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2484,7 +3939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3106,7 +4561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5766,6 +7221,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="106" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="106">
+      <c r="A1" s="156" t="inlineStr">
+        <is>
+          <t>員工編號</t>
+        </is>
+      </c>
+      <c r="B1" s="157" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C1" s="157" t="inlineStr">
+        <is>
+          <t>週銷售數</t>
+        </is>
+      </c>
+      <c r="D1" s="157" t="inlineStr">
+        <is>
+          <t>月銷售數</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1" s="106">
+      <c r="A2" s="158" t="n"/>
+      <c r="B2" s="158" t="n"/>
+      <c r="C2" s="159" t="n"/>
+      <c r="D2" s="159" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1" s="106">
+      <c r="A3" s="158" t="n"/>
+      <c r="B3" s="158" t="n"/>
+      <c r="C3" s="159" t="n"/>
+      <c r="D3" s="159" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" s="106">
+      <c r="A4" s="158" t="n"/>
+      <c r="B4" s="158" t="n"/>
+      <c r="C4" s="159" t="n"/>
+      <c r="D4" s="159" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1" s="106">
+      <c r="A5" s="158" t="n"/>
+      <c r="B5" s="158" t="n"/>
+      <c r="C5" s="160" t="n"/>
+      <c r="D5" s="160" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1" s="106">
+      <c r="A6" s="158" t="n"/>
+      <c r="B6" s="158" t="n"/>
+      <c r="C6" s="160" t="n"/>
+      <c r="D6" s="160" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1" s="106">
+      <c r="A7" s="158" t="n"/>
+      <c r="B7" s="158" t="n"/>
+      <c r="C7" s="160" t="n"/>
+      <c r="D7" s="160" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1" s="106">
+      <c r="A8" s="158" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C8" s="160" t="n"/>
+      <c r="D8" s="160" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A8:B8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.83203125" customWidth="1" style="106" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="106">
+      <c r="A1" s="161" t="inlineStr">
+        <is>
+          <t>員工編號</t>
+        </is>
+      </c>
+      <c r="B1" s="162" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C1" s="162" t="inlineStr">
+        <is>
+          <t>本週銷售數</t>
+        </is>
+      </c>
+      <c r="D1" s="162" t="inlineStr">
+        <is>
+          <t>週銷售金額</t>
+        </is>
+      </c>
+      <c r="E1" s="162" t="inlineStr">
+        <is>
+          <t>月銷售數</t>
+        </is>
+      </c>
+      <c r="F1" s="162" t="inlineStr">
+        <is>
+          <t>月銷售金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="106">
+      <c r="A2" s="163" t="n"/>
+      <c r="B2" s="163" t="n"/>
+      <c r="C2" s="159" t="n"/>
+      <c r="D2" s="159" t="n"/>
+      <c r="E2" s="159" t="n"/>
+      <c r="F2" s="159" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="106">
+      <c r="A3" s="163" t="n"/>
+      <c r="B3" s="163" t="n"/>
+      <c r="C3" s="159" t="n"/>
+      <c r="D3" s="159" t="n"/>
+      <c r="E3" s="164" t="n"/>
+      <c r="F3" s="164" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="106">
+      <c r="A4" s="163" t="n"/>
+      <c r="B4" s="163" t="n"/>
+      <c r="C4" s="159" t="n"/>
+      <c r="D4" s="159" t="n"/>
+      <c r="E4" s="164" t="n"/>
+      <c r="F4" s="164" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" s="106">
+      <c r="A5" s="163" t="n"/>
+      <c r="B5" s="163" t="n"/>
+      <c r="C5" s="164" t="n"/>
+      <c r="D5" s="164" t="n"/>
+      <c r="E5" s="164" t="n"/>
+      <c r="F5" s="164" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="106">
+      <c r="A6" s="163" t="n"/>
+      <c r="B6" s="163" t="n"/>
+      <c r="C6" s="164" t="n"/>
+      <c r="D6" s="164" t="n"/>
+      <c r="E6" s="164" t="n"/>
+      <c r="F6" s="164" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="106">
+      <c r="A7" s="163" t="n"/>
+      <c r="B7" s="163" t="n"/>
+      <c r="C7" s="164" t="n"/>
+      <c r="D7" s="164" t="n"/>
+      <c r="E7" s="164" t="n"/>
+      <c r="F7" s="164" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="106">
+      <c r="A8" s="158" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C8" s="164" t="n"/>
+      <c r="D8" s="164" t="n"/>
+      <c r="E8" s="164" t="n"/>
+      <c r="F8" s="164" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="106">
+      <c r="A9" s="159" t="n"/>
+      <c r="B9" s="159" t="n"/>
+      <c r="C9" s="159" t="n"/>
+      <c r="D9" s="159" t="n"/>
+      <c r="E9" s="159" t="n"/>
+      <c r="F9" s="159" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="106">
+      <c r="A10" s="165" t="inlineStr">
+        <is>
+          <t>年累積金額</t>
+        </is>
+      </c>
+      <c r="B10" s="166" t="inlineStr">
+        <is>
+          <t>xxxxxx</t>
+        </is>
+      </c>
+      <c r="C10" s="159" t="n"/>
+      <c r="D10" s="159" t="n"/>
+      <c r="E10" s="159" t="n"/>
+      <c r="F10" s="159" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A8:B8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -6283,7 +7960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6687,7 +8364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7091,7 +8768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8165,1398 +9842,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" style="106" min="1" max="1"/>
-    <col width="10.5" customWidth="1" style="106" min="2" max="2"/>
-    <col width="10.5" customWidth="1" style="106" min="3" max="3"/>
-    <col width="10.5" customWidth="1" style="106" min="4" max="4"/>
-    <col width="10.5" customWidth="1" style="106" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="106" min="6" max="6"/>
-    <col width="10.5" customWidth="1" style="106" min="7" max="7"/>
-    <col width="10.5" customWidth="1" style="106" min="8" max="8"/>
-    <col width="10.5" customWidth="1" style="106" min="9" max="9"/>
-    <col width="10.5" customWidth="1" style="106" min="10" max="10"/>
-    <col width="10.5" customWidth="1" style="106" min="11" max="11"/>
-    <col width="10.5" customWidth="1" style="106" min="12" max="12"/>
-    <col width="10.5" customWidth="1" style="106" min="13" max="13"/>
-    <col width="10.5" customWidth="1" style="106" min="14" max="14"/>
-    <col width="10.5" customWidth="1" style="106" min="15" max="15"/>
-    <col width="10.5" customWidth="1" style="106" min="16" max="16"/>
-    <col width="10.5" customWidth="1" style="106" min="17" max="17"/>
-    <col width="10.5" customWidth="1" style="106" min="18" max="18"/>
-    <col width="10.5" customWidth="1" style="106" min="19" max="19"/>
-    <col width="10.5" customWidth="1" style="106" min="20" max="20"/>
-    <col width="10.5" customWidth="1" style="106" min="21" max="21"/>
-    <col width="10.5" customWidth="1" style="106" min="22" max="22"/>
-    <col width="10.5" customWidth="1" style="106" min="23" max="23"/>
-    <col width="10.5" customWidth="1" style="106" min="24" max="24"/>
-    <col width="10.5" customWidth="1" style="106" min="25" max="25"/>
-    <col width="10.5" customWidth="1" style="106" min="26" max="26"/>
-    <col width="10.5" customWidth="1" style="106" min="27" max="27"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1" s="106">
-      <c r="A1" s="116" t="inlineStr">
-        <is>
-          <t>士林</t>
-        </is>
-      </c>
-      <c r="B1" s="117" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="C1" s="117" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="D1" s="117" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="E1" s="117" t="inlineStr">
-        <is>
-          <t>CPU
-零搭售</t>
-        </is>
-      </c>
-      <c r="F1" s="118" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="G1" s="119" t="inlineStr">
-        <is>
-          <t>iPhone</t>
-        </is>
-      </c>
-      <c r="H1" s="119" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="I1" s="119" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="J1" s="119" t="inlineStr">
-        <is>
-          <t>iPhone
-零搭售</t>
-        </is>
-      </c>
-      <c r="K1" s="120" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="L1" s="121" t="inlineStr">
-        <is>
-          <t>iPad</t>
-        </is>
-      </c>
-      <c r="M1" s="121" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="N1" s="121" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="O1" s="121" t="inlineStr">
-        <is>
-          <t>iPad
-零搭售</t>
-        </is>
-      </c>
-      <c r="P1" s="122" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="Q1" s="123" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="R1" s="123" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="S1" s="123" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="T1" s="123" t="inlineStr">
-        <is>
-          <t>Watch
-零搭售</t>
-        </is>
-      </c>
-      <c r="U1" s="124" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="V1" s="125" t="inlineStr">
-        <is>
-          <t>AirPods</t>
-        </is>
-      </c>
-      <c r="W1" s="125" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="X1" s="125" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="Y1" s="125" t="inlineStr">
-        <is>
-          <t>AirPods
-零搭售</t>
-        </is>
-      </c>
-      <c r="Z1" s="126" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="AA1" s="127" t="inlineStr">
-        <is>
-          <t>3PP
-搭售率</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1" s="106">
-      <c r="A2" s="128" t="inlineStr">
-        <is>
-          <t>Sam</t>
-        </is>
-      </c>
-      <c r="B2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="130" t="n"/>
-      <c r="E2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="131" t="n"/>
-      <c r="G2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="130" t="n"/>
-      <c r="J2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="131" t="n"/>
-      <c r="L2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="130" t="n"/>
-      <c r="O2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="131" t="n"/>
-      <c r="Q2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="130" t="n"/>
-      <c r="T2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="131" t="n"/>
-      <c r="V2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="130" t="n"/>
-      <c r="Y2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="131" t="n"/>
-      <c r="AA2" s="132" t="n"/>
-    </row>
-    <row r="3" ht="38" customHeight="1" s="106">
-      <c r="A3" s="128" t="inlineStr">
-        <is>
-          <t>Dean</t>
-        </is>
-      </c>
-      <c r="B3" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="140" t="n"/>
-      <c r="E3" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="155" t="n"/>
-      <c r="G3" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" s="134" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L3" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" s="133" t="n">
-        <v>7</v>
-      </c>
-      <c r="N3" s="134" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O3" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" s="133" t="n">
-        <v>6</v>
-      </c>
-      <c r="S3" s="134" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" s="135" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V3" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y3" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA3" s="136" t="n">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1" s="106">
-      <c r="A4" s="128" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="130" t="n"/>
-      <c r="E4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="131" t="n"/>
-      <c r="G4" s="129" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="129" t="n">
-        <v>16</v>
-      </c>
-      <c r="I4" s="137" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="130" t="n"/>
-      <c r="O4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="131" t="n"/>
-      <c r="Q4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="130" t="n"/>
-      <c r="T4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="131" t="n"/>
-      <c r="V4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="130" t="n"/>
-      <c r="Y4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="131" t="n"/>
-      <c r="AA4" s="139" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1" s="106">
-      <c r="A5" s="128" t="inlineStr">
-        <is>
-          <t>Nana</t>
-        </is>
-      </c>
-      <c r="B5" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="134" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="133" t="n">
-        <v>9</v>
-      </c>
-      <c r="I5" s="134" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L5" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="140" t="n"/>
-      <c r="T5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y5" s="133" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="135" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AA5" s="136" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1" s="106">
-      <c r="A6" s="128" t="inlineStr">
-        <is>
-          <t>Zoe</t>
-        </is>
-      </c>
-      <c r="B6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="130" t="n"/>
-      <c r="E6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="131" t="n"/>
-      <c r="G6" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="129" t="n">
-        <v>9</v>
-      </c>
-      <c r="I6" s="137" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="138" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" s="137" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="138" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V6" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="129" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z6" s="138" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AA6" s="139" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1" s="106">
-      <c r="A7" s="128" t="inlineStr">
-        <is>
-          <t>Winter</t>
-        </is>
-      </c>
-      <c r="B7" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="133" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" s="134" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="140" t="n"/>
-      <c r="T7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="155" t="n"/>
-      <c r="V7" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="136" t="n">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1" s="106">
-      <c r="A8" s="128" t="inlineStr">
-        <is>
-          <t>Tanya</t>
-        </is>
-      </c>
-      <c r="B8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="130" t="n"/>
-      <c r="E8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="131" t="n"/>
-      <c r="G8" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="129" t="n">
-        <v>16</v>
-      </c>
-      <c r="I8" s="137" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="J8" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="138" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L8" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" s="129" t="n">
-        <v>9</v>
-      </c>
-      <c r="N8" s="137" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" s="137" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="130" t="n"/>
-      <c r="Y8" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="138" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="139" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1" s="106">
-      <c r="A9" s="141" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B9" s="142" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="142" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="143" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="142" t="n">
-        <v>17</v>
-      </c>
-      <c r="H9" s="142" t="n">
-        <v>62</v>
-      </c>
-      <c r="I9" s="143" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J9" s="142" t="n">
-        <v>6</v>
-      </c>
-      <c r="K9" s="144" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L9" s="142" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" s="142" t="n">
-        <v>25</v>
-      </c>
-      <c r="N9" s="143" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="O9" s="142" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" s="144" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q9" s="142" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" s="142" t="n">
-        <v>12</v>
-      </c>
-      <c r="S9" s="143" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T9" s="142" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" s="144" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="V9" s="142" t="n">
-        <v>4</v>
-      </c>
-      <c r="W9" s="142" t="n">
-        <v>7</v>
-      </c>
-      <c r="X9" s="143" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y9" s="142" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z9" s="144" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AA9" s="145" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1" s="106">
-      <c r="A10" s="146" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="B10" s="147" t="n">
-        <v>23</v>
-      </c>
-      <c r="C10" s="147" t="n">
-        <v>75</v>
-      </c>
-      <c r="D10" s="148" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="E10" s="147" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" s="149" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G10" s="147" t="n">
-        <v>81</v>
-      </c>
-      <c r="H10" s="147" t="n">
-        <v>295</v>
-      </c>
-      <c r="I10" s="148" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="J10" s="147" t="n">
-        <v>45</v>
-      </c>
-      <c r="K10" s="149" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L10" s="147" t="n">
-        <v>51</v>
-      </c>
-      <c r="M10" s="147" t="n">
-        <v>122</v>
-      </c>
-      <c r="N10" s="148" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O10" s="147" t="n">
-        <v>6</v>
-      </c>
-      <c r="P10" s="149" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q10" s="147" t="n">
-        <v>37</v>
-      </c>
-      <c r="R10" s="147" t="n">
-        <v>63</v>
-      </c>
-      <c r="S10" s="148" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T10" s="147" t="n">
-        <v>24</v>
-      </c>
-      <c r="U10" s="149" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="V10" s="147" t="n">
-        <v>45</v>
-      </c>
-      <c r="W10" s="147" t="n">
-        <v>86</v>
-      </c>
-      <c r="X10" s="148" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y10" s="147" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z10" s="149" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AA10" s="150" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1" s="106">
-      <c r="A11" s="146" t="inlineStr">
-        <is>
-          <t>4月</t>
-        </is>
-      </c>
-      <c r="B11" s="151" t="n">
-        <v>14</v>
-      </c>
-      <c r="C11" s="151" t="n">
-        <v>39</v>
-      </c>
-      <c r="D11" s="152" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E11" s="151" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="153" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="151" t="n">
-        <v>62</v>
-      </c>
-      <c r="H11" s="151" t="n">
-        <v>220</v>
-      </c>
-      <c r="I11" s="152" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J11" s="151" t="n">
-        <v>43</v>
-      </c>
-      <c r="K11" s="153" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L11" s="151" t="n">
-        <v>56</v>
-      </c>
-      <c r="M11" s="151" t="n">
-        <v>156</v>
-      </c>
-      <c r="N11" s="152" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O11" s="151" t="n">
-        <v>12</v>
-      </c>
-      <c r="P11" s="153" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="Q11" s="151" t="n">
-        <v>30</v>
-      </c>
-      <c r="R11" s="151" t="n">
-        <v>51</v>
-      </c>
-      <c r="S11" s="152" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T11" s="151" t="n">
-        <v>14</v>
-      </c>
-      <c r="U11" s="153" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="V11" s="151" t="n">
-        <v>37</v>
-      </c>
-      <c r="W11" s="151" t="n">
-        <v>74</v>
-      </c>
-      <c r="X11" s="152" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="151" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z11" s="153" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="AA11" s="154" t="n">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1" s="106">
-      <c r="A12" s="146" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="B12" s="147" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" s="147" t="n">
-        <v>36</v>
-      </c>
-      <c r="D12" s="148" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="147" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="149" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G12" s="147" t="n">
-        <v>79</v>
-      </c>
-      <c r="H12" s="147" t="n">
-        <v>243</v>
-      </c>
-      <c r="I12" s="148" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="J12" s="147" t="n">
-        <v>56</v>
-      </c>
-      <c r="K12" s="149" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L12" s="147" t="n">
-        <v>32</v>
-      </c>
-      <c r="M12" s="147" t="n">
-        <v>87</v>
-      </c>
-      <c r="N12" s="148" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O12" s="147" t="n">
-        <v>9</v>
-      </c>
-      <c r="P12" s="149" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="Q12" s="147" t="n">
-        <v>29</v>
-      </c>
-      <c r="R12" s="147" t="n">
-        <v>45</v>
-      </c>
-      <c r="S12" s="148" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T12" s="147" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" s="149" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="V12" s="147" t="n">
-        <v>48</v>
-      </c>
-      <c r="W12" s="147" t="n">
-        <v>89</v>
-      </c>
-      <c r="X12" s="148" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y12" s="147" t="n">
-        <v>47</v>
-      </c>
-      <c r="Z12" s="149" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AA12" s="150" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col width="17.6640625" customWidth="1" style="106" min="1" max="1"/>
-    <col width="15.1640625" customWidth="1" style="106" min="2" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="57" customHeight="1" s="106">
-      <c r="A1" s="42" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B1" s="43" t="inlineStr">
-        <is>
-          <t>營業額 -(不含SA Care)</t>
-        </is>
-      </c>
-      <c r="C1" s="43" t="inlineStr">
-        <is>
-          <t>3PP 營業額 -(不含SA Care)</t>
-        </is>
-      </c>
-      <c r="D1" s="43" t="inlineStr">
-        <is>
-          <t>原廠商品 -營業額</t>
-        </is>
-      </c>
-      <c r="E1" s="43" t="inlineStr">
-        <is>
-          <t>SA Care -金額(含稅)</t>
-        </is>
-      </c>
-      <c r="F1" s="43" t="inlineStr">
-        <is>
-          <t>純SA Care -搭售率</t>
-        </is>
-      </c>
-      <c r="G1" s="43" t="inlineStr">
-        <is>
-          <t>純3PP 搭售率</t>
-        </is>
-      </c>
-      <c r="H1" s="44" t="inlineStr">
-        <is>
-          <t>原廠商品 -毛利額</t>
-        </is>
-      </c>
-      <c r="I1" s="44" t="inlineStr">
-        <is>
-          <t>3pp商品 -毛利額</t>
-        </is>
-      </c>
-      <c r="J1" s="44" t="inlineStr">
-        <is>
-          <t>SA Care -毛利額</t>
-        </is>
-      </c>
-      <c r="K1" s="45" t="inlineStr">
-        <is>
-          <t>總毛利額</t>
-        </is>
-      </c>
-      <c r="L1" s="44" t="inlineStr">
-        <is>
-          <t>毛利目標</t>
-        </is>
-      </c>
-      <c r="M1" s="44" t="inlineStr">
-        <is>
-          <t>達成率</t>
-        </is>
-      </c>
-      <c r="N1" s="46" t="inlineStr">
-        <is>
-          <t>累計獎金</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="52" customHeight="1" s="106">
-      <c r="A2" s="53" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="115">
-        <f>E2/(E2+B2)</f>
-        <v/>
-      </c>
-      <c r="G2" s="115">
-        <f>C2/B2</f>
-        <v/>
-      </c>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="60">
-        <f>E2/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K2" s="28">
-        <f>H2+I2+J2</f>
-        <v/>
-      </c>
-      <c r="L2" s="28" t="n"/>
-      <c r="M2" s="28" t="n"/>
-      <c r="N2" s="28" t="n"/>
-    </row>
-    <row r="3" ht="52" customHeight="1" s="106">
-      <c r="A3" s="53" t="n"/>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="115">
-        <f>E3/(E3+B3)</f>
-        <v/>
-      </c>
-      <c r="G3" s="115">
-        <f>C3/B3</f>
-        <v/>
-      </c>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="60">
-        <f>E3/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K3" s="28">
-        <f>H3+I3+J3</f>
-        <v/>
-      </c>
-      <c r="L3" s="48" t="n"/>
-      <c r="M3" s="47" t="n"/>
-      <c r="N3" s="48" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1" s="106">
-      <c r="A4" s="53" t="n"/>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="115">
-        <f>E4/(E4+B4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="115">
-        <f>C4/B4</f>
-        <v/>
-      </c>
-      <c r="H4" s="20" t="n"/>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="60">
-        <f>E4/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K4" s="28">
-        <f>H4+I4+J4</f>
-        <v/>
-      </c>
-      <c r="L4" s="48" t="n"/>
-      <c r="M4" s="47" t="n"/>
-      <c r="N4" s="48" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1" s="106">
-      <c r="A5" s="53" t="n"/>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="115">
-        <f>E5/(E5+B5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="115">
-        <f>C5/B5</f>
-        <v/>
-      </c>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="60">
-        <f>E5/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K5" s="28">
-        <f>H5+I5+J5</f>
-        <v/>
-      </c>
-      <c r="L5" s="48" t="n"/>
-      <c r="M5" s="47" t="n"/>
-      <c r="N5" s="48" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1" s="106">
-      <c r="A6" s="53" t="n"/>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="115">
-        <f>E6/(E6+B6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="115">
-        <f>C6/B6</f>
-        <v/>
-      </c>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="60">
-        <f>E6/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K6" s="28">
-        <f>H6+I6+J6</f>
-        <v/>
-      </c>
-      <c r="L6" s="48" t="n"/>
-      <c r="M6" s="47" t="n"/>
-      <c r="N6" s="48" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1" s="106">
-      <c r="A7" s="53" t="n"/>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="115">
-        <f>E7/(E7+B7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="115">
-        <f>C7/B7</f>
-        <v/>
-      </c>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="60">
-        <f>E7/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K7" s="28">
-        <f>H7+I7+J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="48" t="n"/>
-      <c r="M7" s="47" t="n"/>
-      <c r="N7" s="48" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1" s="106">
-      <c r="A8" s="53" t="n"/>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="115">
-        <f>E8/(E8+B8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="115">
-        <f>C8/B8</f>
-        <v/>
-      </c>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="60">
-        <f>E8/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K8" s="28">
-        <f>H8+I8+J8</f>
-        <v/>
-      </c>
-      <c r="L8" s="48" t="n"/>
-      <c r="M8" s="47" t="n"/>
-      <c r="N8" s="48" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1" s="106">
-      <c r="A9" s="49" t="inlineStr">
-        <is>
-          <t>加總</t>
-        </is>
-      </c>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="115">
-        <f>E9/(E9+B9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="115">
-        <f>C9/B9</f>
-        <v/>
-      </c>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="60">
-        <f>E9/2/1.05</f>
-        <v/>
-      </c>
-      <c r="K9" s="28">
-        <f>H9+I9+J9</f>
-        <v/>
-      </c>
-      <c r="L9" s="48" t="n"/>
-      <c r="M9" s="47" t="n"/>
-      <c r="N9" s="28" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/週報模板.xlsx
+++ b/週報模板.xlsx
@@ -228,7 +228,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -420,6 +420,11 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -703,7 +708,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1190,6 +1195,15 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3115,12 +3129,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="10.33203125" customWidth="1" style="106" min="2" max="9"/>
     <col width="11.1640625" customWidth="1" style="106" min="10" max="10"/>
     <col width="10.33203125" customWidth="1" style="106" min="11" max="22"/>
+    <col width="10.33203125" customWidth="1" style="106" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="106">
@@ -3235,6 +3250,11 @@
       <c r="V1" s="68" t="inlineStr">
         <is>
           <t>搭售率</t>
+        </is>
+      </c>
+      <c r="X1" s="167" t="inlineStr">
+        <is>
+          <t>服務費</t>
         </is>
       </c>
     </row>
@@ -3285,6 +3305,7 @@
       <c r="T3" s="50" t="n"/>
       <c r="U3" s="50" t="n"/>
       <c r="V3" s="51" t="n"/>
+      <c r="X3" s="168" t="n"/>
     </row>
     <row r="4" ht="39" customHeight="1" s="106">
       <c r="A4" s="53" t="n"/>
@@ -3309,6 +3330,7 @@
       <c r="T4" s="50" t="n"/>
       <c r="U4" s="50" t="n"/>
       <c r="V4" s="51" t="n"/>
+      <c r="X4" s="168" t="n"/>
     </row>
     <row r="5" ht="39" customHeight="1" s="106">
       <c r="A5" s="53" t="n"/>
@@ -3333,6 +3355,7 @@
       <c r="T5" s="50" t="n"/>
       <c r="U5" s="50" t="n"/>
       <c r="V5" s="51" t="n"/>
+      <c r="X5" s="168" t="n"/>
     </row>
     <row r="6" ht="39" customHeight="1" s="106">
       <c r="A6" s="53" t="n"/>
@@ -3357,6 +3380,7 @@
       <c r="T6" s="50" t="n"/>
       <c r="U6" s="50" t="n"/>
       <c r="V6" s="51" t="n"/>
+      <c r="X6" s="168" t="n"/>
     </row>
     <row r="7" ht="39" customHeight="1" s="106">
       <c r="A7" s="53" t="n"/>
@@ -3381,6 +3405,7 @@
       <c r="T7" s="50" t="n"/>
       <c r="U7" s="50" t="n"/>
       <c r="V7" s="51" t="n"/>
+      <c r="X7" s="168" t="n"/>
     </row>
     <row r="8" ht="39" customHeight="1" s="106">
       <c r="A8" s="53" t="n"/>
@@ -3405,6 +3430,7 @@
       <c r="T8" s="50" t="n"/>
       <c r="U8" s="50" t="n"/>
       <c r="V8" s="51" t="n"/>
+      <c r="X8" s="168" t="n"/>
     </row>
     <row r="9" ht="19" customHeight="1" s="106">
       <c r="A9" s="41" t="inlineStr">
@@ -3433,6 +3459,7 @@
       <c r="T9" s="41" t="n"/>
       <c r="U9" s="41" t="n"/>
       <c r="V9" s="51" t="n"/>
+      <c r="X9" s="169" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3445,12 +3472,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="10.33203125" customWidth="1" style="106" min="2" max="9"/>
     <col width="11.1640625" customWidth="1" style="106" min="10" max="10"/>
     <col width="10.33203125" customWidth="1" style="106" min="11" max="22"/>
+    <col width="10.33203125" customWidth="1" style="106" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="106">
@@ -3565,6 +3593,11 @@
       <c r="V1" s="68" t="inlineStr">
         <is>
           <t>搭售率</t>
+        </is>
+      </c>
+      <c r="X1" s="167" t="inlineStr">
+        <is>
+          <t>服務費</t>
         </is>
       </c>
     </row>
@@ -3615,6 +3648,7 @@
       <c r="T3" s="50" t="n"/>
       <c r="U3" s="50" t="n"/>
       <c r="V3" s="51" t="n"/>
+      <c r="X3" s="168" t="n"/>
     </row>
     <row r="4" ht="39" customHeight="1" s="106">
       <c r="A4" s="53" t="n"/>
@@ -3639,6 +3673,7 @@
       <c r="T4" s="50" t="n"/>
       <c r="U4" s="50" t="n"/>
       <c r="V4" s="51" t="n"/>
+      <c r="X4" s="168" t="n"/>
     </row>
     <row r="5" ht="39" customHeight="1" s="106">
       <c r="A5" s="53" t="n"/>
@@ -3663,6 +3698,7 @@
       <c r="T5" s="50" t="n"/>
       <c r="U5" s="50" t="n"/>
       <c r="V5" s="51" t="n"/>
+      <c r="X5" s="168" t="n"/>
     </row>
     <row r="6" ht="39" customHeight="1" s="106">
       <c r="A6" s="53" t="n"/>
@@ -3687,6 +3723,7 @@
       <c r="T6" s="50" t="n"/>
       <c r="U6" s="50" t="n"/>
       <c r="V6" s="51" t="n"/>
+      <c r="X6" s="168" t="n"/>
     </row>
     <row r="7" ht="39" customHeight="1" s="106">
       <c r="A7" s="53" t="n"/>
@@ -3711,6 +3748,7 @@
       <c r="T7" s="50" t="n"/>
       <c r="U7" s="50" t="n"/>
       <c r="V7" s="51" t="n"/>
+      <c r="X7" s="168" t="n"/>
     </row>
     <row r="8" ht="39" customHeight="1" s="106">
       <c r="A8" s="53" t="n"/>
@@ -3735,6 +3773,7 @@
       <c r="T8" s="50" t="n"/>
       <c r="U8" s="50" t="n"/>
       <c r="V8" s="51" t="n"/>
+      <c r="X8" s="168" t="n"/>
     </row>
     <row r="9" ht="19" customHeight="1" s="106">
       <c r="A9" s="41" t="inlineStr">
@@ -3763,6 +3802,7 @@
       <c r="T9" s="41" t="n"/>
       <c r="U9" s="41" t="n"/>
       <c r="V9" s="51" t="n"/>
+      <c r="X9" s="169" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/週報模板.xlsx
+++ b/週報模板.xlsx
@@ -8,21 +8,22 @@
   <sheets>
     <sheet name="設定" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1.主機銷售台數" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2.每月重點" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3.Speakers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4.門市人流" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5.門市週報" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6.3PP配件比較" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7.3PP 銷售排名" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8.VAP銷售排名" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="9.搭售統計_週" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10.搭售統計_月" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11.個人新制獎金" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12.個人週主機" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13.個人月主機" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14.個人月3PP" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="15.月報YOY" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="16.3PP YOY" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2.教育價" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3.每月重點" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4.Speakers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5.門市人流" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6.門市週報" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7.3PP配件比較" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8.3PP 銷售排名" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9.VAP銷售排名" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10.搭售統計_週" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11.搭售統計_月" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12.個人新制獎金" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13.個人週主機" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14.個人月主機" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15.個人月3PP" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16.月報YOY" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17.3PP YOY" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -238,7 +239,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -450,6 +451,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.9"/>
       </patternFill>
     </fill>
   </fills>
@@ -733,7 +739,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1255,6 +1261,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1787,1069 +1796,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="106" min="1" max="1"/>
-    <col width="10.5" customWidth="1" style="106" min="2" max="2"/>
-    <col width="10.5" customWidth="1" style="106" min="3" max="3"/>
-    <col width="10.5" customWidth="1" style="106" min="4" max="4"/>
-    <col width="10.5" customWidth="1" style="106" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="106" min="6" max="6"/>
-    <col width="10.5" customWidth="1" style="106" min="7" max="7"/>
-    <col width="10.5" customWidth="1" style="106" min="8" max="8"/>
-    <col width="10.5" customWidth="1" style="106" min="9" max="9"/>
-    <col width="10.5" customWidth="1" style="106" min="10" max="10"/>
-    <col width="10.5" customWidth="1" style="106" min="11" max="11"/>
-    <col width="10.5" customWidth="1" style="106" min="12" max="12"/>
-    <col width="10.5" customWidth="1" style="106" min="13" max="13"/>
-    <col width="10.5" customWidth="1" style="106" min="14" max="14"/>
-    <col width="10.5" customWidth="1" style="106" min="15" max="15"/>
-    <col width="10.5" customWidth="1" style="106" min="16" max="16"/>
-    <col width="10.5" customWidth="1" style="106" min="17" max="17"/>
-    <col width="10.5" customWidth="1" style="106" min="18" max="18"/>
-    <col width="10.5" customWidth="1" style="106" min="19" max="19"/>
-    <col width="10.5" customWidth="1" style="106" min="20" max="20"/>
-    <col width="10.5" customWidth="1" style="106" min="21" max="21"/>
-    <col width="10.5" customWidth="1" style="106" min="22" max="22"/>
-    <col width="10.5" customWidth="1" style="106" min="23" max="23"/>
-    <col width="10.5" customWidth="1" style="106" min="24" max="24"/>
-    <col width="10.5" customWidth="1" style="106" min="25" max="25"/>
-    <col width="10.5" customWidth="1" style="106" min="26" max="26"/>
-    <col width="10.5" customWidth="1" style="106" min="27" max="27"/>
+    <col width="18.33203125" customWidth="1" style="106" min="2" max="2"/>
+    <col width="93" customWidth="1" style="106" min="3" max="3"/>
+    <col width="19.6640625" customWidth="1" style="106" min="5" max="5"/>
+    <col width="92.33203125" customWidth="1" style="106" min="6" max="6"/>
+    <col width="19" bestFit="1" customWidth="1" style="106" min="7" max="7"/>
+    <col width="19.1640625" customWidth="1" style="106" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" s="106">
-      <c r="A1" s="116" t="inlineStr">
-        <is>
-          <t>士林</t>
-        </is>
-      </c>
-      <c r="B1" s="117" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="C1" s="117" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="D1" s="117" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="E1" s="117" t="inlineStr">
-        <is>
-          <t>CPU
-零搭售</t>
-        </is>
-      </c>
-      <c r="F1" s="118" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="G1" s="119" t="inlineStr">
-        <is>
-          <t>iPhone</t>
-        </is>
-      </c>
-      <c r="H1" s="119" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="I1" s="119" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="J1" s="119" t="inlineStr">
-        <is>
-          <t>iPhone
-零搭售</t>
-        </is>
-      </c>
-      <c r="K1" s="120" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="L1" s="121" t="inlineStr">
-        <is>
-          <t>iPad</t>
-        </is>
-      </c>
-      <c r="M1" s="121" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="N1" s="121" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="O1" s="121" t="inlineStr">
-        <is>
-          <t>iPad
-零搭售</t>
-        </is>
-      </c>
-      <c r="P1" s="122" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="Q1" s="123" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="R1" s="123" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="S1" s="123" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="T1" s="123" t="inlineStr">
-        <is>
-          <t>Watch
-零搭售</t>
-        </is>
-      </c>
-      <c r="U1" s="124" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="V1" s="125" t="inlineStr">
-        <is>
-          <t>AirPods</t>
-        </is>
-      </c>
-      <c r="W1" s="125" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="X1" s="125" t="inlineStr">
-        <is>
-          <t>搭售率</t>
-        </is>
-      </c>
-      <c r="Y1" s="125" t="inlineStr">
-        <is>
-          <t>AirPods
-零搭售</t>
-        </is>
-      </c>
-      <c r="Z1" s="126" t="inlineStr">
-        <is>
-          <t>零搭售
-比例</t>
-        </is>
-      </c>
-      <c r="AA1" s="127" t="inlineStr">
-        <is>
-          <t>3PP
-搭售率</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1" s="106">
-      <c r="A2" s="128" t="inlineStr">
-        <is>
-          <t>Sam</t>
-        </is>
-      </c>
-      <c r="B2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="130" t="n"/>
-      <c r="E2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="131" t="n"/>
-      <c r="G2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="130" t="n"/>
-      <c r="J2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="131" t="n"/>
-      <c r="L2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="130" t="n"/>
-      <c r="O2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="131" t="n"/>
-      <c r="Q2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="130" t="n"/>
-      <c r="T2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="131" t="n"/>
-      <c r="V2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="130" t="n"/>
-      <c r="Y2" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="131" t="n"/>
-      <c r="AA2" s="132" t="n"/>
-    </row>
-    <row r="3" ht="38" customHeight="1" s="106">
-      <c r="A3" s="128" t="inlineStr">
-        <is>
-          <t>Dean</t>
-        </is>
-      </c>
-      <c r="B3" s="133" t="n">
+    <row r="1" ht="38" customHeight="1" s="106">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B1" s="38" t="inlineStr">
+        <is>
+          <t>存貨代碼</t>
+        </is>
+      </c>
+      <c r="C1" s="38" t="inlineStr">
+        <is>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="D1" s="38" t="inlineStr">
+        <is>
+          <t>週銷累計 數量</t>
+        </is>
+      </c>
+      <c r="E1" s="38" t="inlineStr">
+        <is>
+          <t>存貨代碼</t>
+        </is>
+      </c>
+      <c r="F1" s="38" t="inlineStr">
+        <is>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="G1" s="38" t="inlineStr">
+        <is>
+          <t>月銷累計 數量</t>
+        </is>
+      </c>
+      <c r="H1" s="38" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="49" customHeight="1" s="106">
+      <c r="A2" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="133" t="n">
+      <c r="B2" s="40" t="inlineStr">
+        <is>
+          <t>5902002</t>
+        </is>
+      </c>
+      <c r="C2" s="40" t="inlineStr">
+        <is>
+          <t>pqi iPhone 17 Pro 康寧鋼化玻璃保護貼 2.5D</t>
+        </is>
+      </c>
+      <c r="D2" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="40" t="inlineStr">
+        <is>
+          <t>5902002</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>pqi iPhone 17 Pro 康寧鋼化玻璃保護貼 2.5D</t>
+        </is>
+      </c>
+      <c r="G2" s="113" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="114" t="n">
+        <v>6490</v>
+      </c>
+    </row>
+    <row r="3" ht="49" customHeight="1" s="106">
+      <c r="A3" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="40" t="inlineStr">
+        <is>
+          <t>5901984</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="inlineStr">
+        <is>
+          <t>pqi-45W GaN氮化镓(2C)充電器MC32-白色</t>
+        </is>
+      </c>
+      <c r="D3" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="40" t="inlineStr">
+        <is>
+          <t>22400301</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>維修專用-裸裝滿版玻璃保貼iPhone 14 Pro Max</t>
+        </is>
+      </c>
+      <c r="G3" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="114" t="n">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="4" ht="49" customHeight="1" s="106">
+      <c r="A4" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>5901995</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="inlineStr">
+        <is>
+          <t>pqi AirPods Pro 3 皮革保護殼 - 黑色</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="40" t="inlineStr">
+        <is>
+          <t>46200219</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>pqi iPad (A16) 11吋 玻璃保護貼</t>
+        </is>
+      </c>
+      <c r="G4" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="114" t="n">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="5" ht="49" customHeight="1" s="106">
+      <c r="A5" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>5902003</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>pqi iPhone 17 Pro Max 康寧鋼化玻璃保護貼 2.5D</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>46200232</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>pqi iPhone 17 Pro / Pro Max 鏡頭貼 深藍</t>
+        </is>
+      </c>
+      <c r="G5" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="114" t="n">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="6" ht="49" customHeight="1" s="106">
+      <c r="A6" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>22400301</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>維修專用-裸裝滿版玻璃保貼iPhone 14 Pro Max</t>
+        </is>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="40" t="inlineStr">
+        <is>
+          <t>5901984</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>pqi-45W GaN氮化镓(2C)充電器MC32-白色</t>
+        </is>
+      </c>
+      <c r="G6" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="114" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="7" ht="49" customHeight="1" s="106">
+      <c r="A7" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>46200123</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>VAP-iPad mini 8.3吋 (6/A17 Pro) 玻璃保護貼</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="40" t="inlineStr">
+        <is>
+          <t>5901995</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>pqi AirPods Pro 3 皮革保護殼 - 黑色</t>
+        </is>
+      </c>
+      <c r="G7" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="114" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="8" ht="49" customHeight="1" s="106">
+      <c r="A8" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>46200168</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>VAP-MacBook Pro 14吋亮面保護貼</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="40" t="inlineStr">
+        <is>
+          <t>5902003</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>pqi iPhone 17 Pro Max 康寧鋼化玻璃保護貼 2.5D</t>
+        </is>
+      </c>
+      <c r="G8" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="114" t="n">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="9" ht="49" customHeight="1" s="106">
+      <c r="A9" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="D3" s="134" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" s="133" t="n">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>46200211</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>@VAP iPhone 16e 玻璃保護貼</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="133" t="n">
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>46200123</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>VAP-iPad mini 8.3吋 (6/A17 Pro) 玻璃保護貼</t>
+        </is>
+      </c>
+      <c r="G9" s="113" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" s="134" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="135" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L3" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" s="133" t="n">
-        <v>7</v>
-      </c>
-      <c r="N3" s="134" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O3" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" s="133" t="n">
-        <v>6</v>
-      </c>
-      <c r="S3" s="134" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" s="133" t="n">
+      <c r="H9" s="114" t="n">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="10" ht="49" customHeight="1" s="106">
+      <c r="A10" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>46200217</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>@pqi-iPad Air 11吋 (M3/M4)-玻璃保護貼</t>
+        </is>
+      </c>
+      <c r="D10" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="U3" s="135" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V3" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="X3" s="134" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y3" s="133" t="n">
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>46200168</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>VAP-MacBook Pro 14吋亮面保護貼</t>
+        </is>
+      </c>
+      <c r="G10" s="113" t="n">
         <v>1</v>
       </c>
-      <c r="Z3" s="135" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AA3" s="136" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1" s="106">
-      <c r="A4" s="128" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="130" t="n"/>
-      <c r="E4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="131" t="n"/>
-      <c r="G4" s="129" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="129" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="137" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="J4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="130" t="n"/>
-      <c r="O4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="131" t="n"/>
-      <c r="Q4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="129" t="n">
+      <c r="H10" s="114" t="n">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="11" ht="49" customHeight="1" s="106">
+      <c r="A11" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>46200229</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>pqi iPhone 17 Pro / Pro Max 鏡頭貼 銀</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="S4" s="130" t="n"/>
-      <c r="T4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="131" t="n"/>
-      <c r="V4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="130" t="n"/>
-      <c r="Y4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="131" t="n"/>
-      <c r="AA4" s="139" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1" s="106">
-      <c r="A5" s="128" t="inlineStr">
-        <is>
-          <t>Nana</t>
-        </is>
-      </c>
-      <c r="B5" s="133" t="n">
+      <c r="E11" s="40" t="inlineStr">
+        <is>
+          <t>46200211</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>@VAP iPhone 16e 玻璃保護貼</t>
+        </is>
+      </c>
+      <c r="G11" s="113" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="134" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="133" t="n">
-        <v>9</v>
-      </c>
-      <c r="I5" s="134" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L5" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="140" t="n"/>
-      <c r="T5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y5" s="133" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="135" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AA5" s="136" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1" s="106">
-      <c r="A6" s="128" t="inlineStr">
-        <is>
-          <t>Zoe</t>
-        </is>
-      </c>
-      <c r="B6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="130" t="n"/>
-      <c r="E6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="131" t="n"/>
-      <c r="G6" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="129" t="n">
-        <v>9</v>
-      </c>
-      <c r="I6" s="137" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="138" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L6" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" s="129" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" s="137" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O6" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="138" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="X6" s="137" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y6" s="129" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z6" s="138" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AA6" s="139" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1" s="106">
-      <c r="A7" s="128" t="inlineStr">
-        <is>
-          <t>Winter</t>
-        </is>
-      </c>
-      <c r="B7" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="133" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" s="134" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="135" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q7" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" s="133" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" s="134" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="136" t="n">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1" s="106">
-      <c r="A8" s="128" t="inlineStr">
-        <is>
-          <t>Tanya</t>
-        </is>
-      </c>
-      <c r="B8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="130" t="n"/>
-      <c r="E8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="131" t="n"/>
-      <c r="G8" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="129" t="n">
-        <v>24</v>
-      </c>
-      <c r="I8" s="137" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="138" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L8" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" s="129" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" s="137" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" s="137" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="130" t="n"/>
-      <c r="Y8" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="138" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="139" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1" s="106">
-      <c r="A9" s="141" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B9" s="142" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="142" t="n">
-        <v>14</v>
-      </c>
-      <c r="D9" s="143" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="E9" s="142" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="144" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G9" s="142" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="142" t="n">
-        <v>76</v>
-      </c>
-      <c r="I9" s="143" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J9" s="142" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="144" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L9" s="142" t="n">
-        <v>13</v>
-      </c>
-      <c r="M9" s="142" t="n">
-        <v>27</v>
-      </c>
-      <c r="N9" s="143" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O9" s="142" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" s="144" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q9" s="142" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" s="142" t="n">
-        <v>13</v>
-      </c>
-      <c r="S9" s="143" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T9" s="142" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" s="144" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V9" s="142" t="n">
-        <v>6</v>
-      </c>
-      <c r="W9" s="142" t="n">
-        <v>11</v>
-      </c>
-      <c r="X9" s="143" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y9" s="142" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z9" s="144" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AA9" s="145" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1" s="106">
-      <c r="A10" s="146" t="inlineStr">
-        <is>
-          <t>Ｗ9</t>
-        </is>
-      </c>
-      <c r="B10" s="147" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="147" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" s="148" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="E10" s="147" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="149" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G10" s="147" t="n">
-        <v>14</v>
-      </c>
-      <c r="H10" s="147" t="n">
-        <v>40</v>
-      </c>
-      <c r="I10" s="148" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J10" s="147" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="149" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L10" s="147" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" s="147" t="n">
-        <v>24</v>
-      </c>
-      <c r="N10" s="148" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O10" s="147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="147" t="n">
-        <v>10</v>
-      </c>
-      <c r="R10" s="147" t="n">
-        <v>19</v>
-      </c>
-      <c r="S10" s="148" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T10" s="147" t="n">
-        <v>7</v>
-      </c>
-      <c r="U10" s="149" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="V10" s="147" t="n">
-        <v>11</v>
-      </c>
-      <c r="W10" s="147" t="n">
-        <v>22</v>
-      </c>
-      <c r="X10" s="148" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y10" s="147" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" s="149" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AA10" s="150" t="n">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1" s="106">
-      <c r="A11" s="146" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B11" s="151" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" s="151" t="n">
-        <v>18</v>
-      </c>
-      <c r="D11" s="152" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E11" s="151" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="153" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G11" s="151" t="n">
-        <v>14</v>
-      </c>
-      <c r="H11" s="151" t="n">
-        <v>54</v>
-      </c>
-      <c r="I11" s="152" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="J11" s="151" t="n">
-        <v>8</v>
-      </c>
-      <c r="K11" s="153" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L11" s="151" t="n">
-        <v>18</v>
-      </c>
-      <c r="M11" s="151" t="n">
-        <v>40</v>
-      </c>
-      <c r="N11" s="152" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O11" s="151" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" s="153" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Q11" s="151" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" s="151" t="n">
-        <v>14</v>
-      </c>
-      <c r="S11" s="152" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T11" s="151" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" s="153" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="V11" s="151" t="n">
-        <v>12</v>
-      </c>
-      <c r="W11" s="151" t="n">
-        <v>26</v>
-      </c>
-      <c r="X11" s="152" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y11" s="151" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z11" s="153" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AA11" s="154" t="n">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1" s="106">
-      <c r="A12" s="146" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B12" s="147" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="147" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="147" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="149" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G12" s="147" t="n">
-        <v>17</v>
-      </c>
-      <c r="H12" s="147" t="n">
-        <v>62</v>
-      </c>
-      <c r="I12" s="148" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J12" s="147" t="n">
-        <v>14</v>
-      </c>
-      <c r="K12" s="149" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L12" s="147" t="n">
-        <v>16</v>
-      </c>
-      <c r="M12" s="147" t="n">
-        <v>48</v>
-      </c>
-      <c r="N12" s="148" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" s="147" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" s="149" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q12" s="147" t="n">
-        <v>9</v>
-      </c>
-      <c r="R12" s="147" t="n">
-        <v>20</v>
-      </c>
-      <c r="S12" s="148" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T12" s="147" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" s="149" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="V12" s="147" t="n">
-        <v>11</v>
-      </c>
-      <c r="W12" s="147" t="n">
-        <v>27</v>
-      </c>
-      <c r="X12" s="148" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y12" s="147" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="149" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AA12" s="150" t="n">
-        <v>2.93</v>
+      <c r="H11" s="114" t="n">
+        <v>981</v>
       </c>
     </row>
   </sheetData>
@@ -3113,16 +2450,20 @@
         </is>
       </c>
       <c r="B3" s="133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="140" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D3" s="134" t="n">
+        <v>8</v>
+      </c>
       <c r="E3" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="155" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F3" s="135" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G3" s="133" t="n">
         <v>1</v>
       </c>
@@ -3133,10 +2474,10 @@
         <v>4</v>
       </c>
       <c r="J3" s="133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="135" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="L3" s="133" t="n">
         <v>3</v>
@@ -3169,22 +2510,22 @@
         <v>0.33</v>
       </c>
       <c r="V3" s="133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" s="133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X3" s="134" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Y3" s="133" t="n">
         <v>1</v>
       </c>
       <c r="Z3" s="135" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AA3" s="136" t="n">
-        <v>2.71</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1" s="106">
@@ -3205,13 +2546,13 @@
       </c>
       <c r="F4" s="131" t="n"/>
       <c r="G4" s="129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="129" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I4" s="137" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="J4" s="129" t="n">
         <v>0</v>
@@ -3253,7 +2594,7 @@
       </c>
       <c r="Z4" s="131" t="n"/>
       <c r="AA4" s="139" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" s="106">
@@ -3372,13 +2713,13 @@
         <v>0.4</v>
       </c>
       <c r="L6" s="129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" s="137" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O6" s="129" t="n">
         <v>0</v>
@@ -3402,19 +2743,19 @@
         <v>0.33</v>
       </c>
       <c r="V6" s="129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W6" s="129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X6" s="137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="129" t="n">
         <v>5</v>
       </c>
       <c r="Z6" s="138" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AA6" s="139" t="n">
         <v>2</v>
@@ -3436,19 +2777,19 @@
         <v>2</v>
       </c>
       <c r="E7" s="133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="135" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="133" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7" s="134" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="J7" s="133" t="n">
         <v>0</v>
@@ -3472,16 +2813,20 @@
         <v>0.5</v>
       </c>
       <c r="Q7" s="133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="140" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S7" s="134" t="n">
+        <v>1</v>
+      </c>
       <c r="T7" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="U7" s="155" t="n"/>
+      <c r="U7" s="135" t="n">
+        <v>0</v>
+      </c>
       <c r="V7" s="133" t="n">
         <v>1</v>
       </c>
@@ -3498,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="AA7" s="136" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" s="106">
@@ -3519,28 +2864,28 @@
       </c>
       <c r="F8" s="131" t="n"/>
       <c r="G8" s="129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="129" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I8" s="137" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="J8" s="129" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="138" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L8" s="129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" s="129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" s="137" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O8" s="129" t="n">
         <v>0</v>
@@ -3571,13 +2916,13 @@
       </c>
       <c r="X8" s="130" t="n"/>
       <c r="Y8" s="129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="138" t="n">
         <v>1</v>
       </c>
       <c r="AA8" s="139" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" s="106">
@@ -3587,337 +2932,337 @@
         </is>
       </c>
       <c r="B9" s="142" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="142" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" s="143" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E9" s="142" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="142" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="143" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="142" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" s="144" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="142" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H9" s="142" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I9" s="143" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J9" s="142" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K9" s="144" t="n">
         <v>0.26</v>
       </c>
       <c r="L9" s="142" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M9" s="142" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N9" s="143" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="O9" s="142" t="n">
         <v>2</v>
       </c>
       <c r="P9" s="144" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="Q9" s="142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R9" s="142" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S9" s="143" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="T9" s="142" t="n">
         <v>4</v>
       </c>
       <c r="U9" s="144" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V9" s="142" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W9" s="142" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="X9" s="143" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Y9" s="142" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z9" s="144" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="AA9" s="145" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" s="106">
       <c r="A10" s="146" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>Ｗ9</t>
         </is>
       </c>
       <c r="B10" s="147" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C10" s="147" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D10" s="148" t="n">
-        <v>3.26</v>
+        <v>3.67</v>
       </c>
       <c r="E10" s="147" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="149" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G10" s="147" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" s="147" t="n">
+        <v>40</v>
+      </c>
+      <c r="I10" s="148" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J10" s="147" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="149" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L10" s="147" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" s="147" t="n">
+        <v>24</v>
+      </c>
+      <c r="N10" s="148" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O10" s="147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="147" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" s="147" t="n">
+        <v>19</v>
+      </c>
+      <c r="S10" s="148" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T10" s="147" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" s="149" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="V10" s="147" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="149" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G10" s="147" t="n">
-        <v>81</v>
-      </c>
-      <c r="H10" s="147" t="n">
-        <v>295</v>
-      </c>
-      <c r="I10" s="148" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="J10" s="147" t="n">
-        <v>45</v>
-      </c>
-      <c r="K10" s="149" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L10" s="147" t="n">
-        <v>51</v>
-      </c>
-      <c r="M10" s="147" t="n">
-        <v>122</v>
-      </c>
-      <c r="N10" s="148" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O10" s="147" t="n">
-        <v>6</v>
-      </c>
-      <c r="P10" s="149" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q10" s="147" t="n">
-        <v>37</v>
-      </c>
-      <c r="R10" s="147" t="n">
-        <v>63</v>
-      </c>
-      <c r="S10" s="148" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T10" s="147" t="n">
-        <v>24</v>
-      </c>
-      <c r="U10" s="149" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="V10" s="147" t="n">
-        <v>45</v>
-      </c>
       <c r="W10" s="147" t="n">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="X10" s="148" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Y10" s="147" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="Z10" s="149" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="AA10" s="150" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" s="106">
       <c r="A11" s="146" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B11" s="151" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="151" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" s="152" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E11" s="151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="153" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G11" s="151" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="151" t="n">
-        <v>39</v>
-      </c>
-      <c r="D11" s="152" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E11" s="151" t="n">
+      <c r="H11" s="151" t="n">
+        <v>54</v>
+      </c>
+      <c r="I11" s="152" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="J11" s="151" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="153" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L11" s="151" t="n">
+        <v>18</v>
+      </c>
+      <c r="M11" s="151" t="n">
+        <v>40</v>
+      </c>
+      <c r="N11" s="152" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O11" s="151" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" s="153" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q11" s="151" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" s="151" t="n">
         <v>14</v>
       </c>
-      <c r="F11" s="153" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="151" t="n">
-        <v>62</v>
-      </c>
-      <c r="H11" s="151" t="n">
-        <v>220</v>
-      </c>
-      <c r="I11" s="152" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J11" s="151" t="n">
-        <v>43</v>
-      </c>
-      <c r="K11" s="153" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L11" s="151" t="n">
-        <v>56</v>
-      </c>
-      <c r="M11" s="151" t="n">
-        <v>156</v>
-      </c>
-      <c r="N11" s="152" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O11" s="151" t="n">
+      <c r="S11" s="152" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T11" s="151" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" s="153" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="V11" s="151" t="n">
         <v>12</v>
       </c>
-      <c r="P11" s="153" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="Q11" s="151" t="n">
-        <v>30</v>
-      </c>
-      <c r="R11" s="151" t="n">
-        <v>51</v>
-      </c>
-      <c r="S11" s="152" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T11" s="151" t="n">
-        <v>14</v>
-      </c>
-      <c r="U11" s="153" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="V11" s="151" t="n">
-        <v>37</v>
-      </c>
       <c r="W11" s="151" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="X11" s="152" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Y11" s="151" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="Z11" s="153" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="AA11" s="154" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" s="106">
       <c r="A12" s="146" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B12" s="147" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C12" s="147" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D12" s="148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="147" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="149" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G12" s="147" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" s="147" t="n">
+        <v>62</v>
+      </c>
+      <c r="I12" s="148" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J12" s="147" t="n">
+        <v>14</v>
+      </c>
+      <c r="K12" s="149" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L12" s="147" t="n">
+        <v>16</v>
+      </c>
+      <c r="M12" s="147" t="n">
+        <v>48</v>
+      </c>
+      <c r="N12" s="148" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="147" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="149" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G12" s="147" t="n">
-        <v>79</v>
-      </c>
-      <c r="H12" s="147" t="n">
-        <v>243</v>
-      </c>
-      <c r="I12" s="148" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="J12" s="147" t="n">
-        <v>56</v>
-      </c>
-      <c r="K12" s="149" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L12" s="147" t="n">
-        <v>32</v>
-      </c>
-      <c r="M12" s="147" t="n">
-        <v>87</v>
-      </c>
-      <c r="N12" s="148" t="n">
-        <v>2.72</v>
-      </c>
       <c r="O12" s="147" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" s="149" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q12" s="147" t="n">
         <v>9</v>
       </c>
-      <c r="P12" s="149" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="Q12" s="147" t="n">
-        <v>29</v>
-      </c>
       <c r="R12" s="147" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="S12" s="148" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="T12" s="147" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U12" s="149" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="V12" s="147" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="W12" s="147" t="n">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="X12" s="148" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" s="147" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="Z12" s="149" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="AA12" s="150" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
     </row>
   </sheetData>
@@ -3926,6 +3271,1074 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" style="106" min="1" max="1"/>
+    <col width="10.5" customWidth="1" style="106" min="2" max="2"/>
+    <col width="10.5" customWidth="1" style="106" min="3" max="3"/>
+    <col width="10.5" customWidth="1" style="106" min="4" max="4"/>
+    <col width="10.5" customWidth="1" style="106" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="106" min="6" max="6"/>
+    <col width="10.5" customWidth="1" style="106" min="7" max="7"/>
+    <col width="10.5" customWidth="1" style="106" min="8" max="8"/>
+    <col width="10.5" customWidth="1" style="106" min="9" max="9"/>
+    <col width="10.5" customWidth="1" style="106" min="10" max="10"/>
+    <col width="10.5" customWidth="1" style="106" min="11" max="11"/>
+    <col width="10.5" customWidth="1" style="106" min="12" max="12"/>
+    <col width="10.5" customWidth="1" style="106" min="13" max="13"/>
+    <col width="10.5" customWidth="1" style="106" min="14" max="14"/>
+    <col width="10.5" customWidth="1" style="106" min="15" max="15"/>
+    <col width="10.5" customWidth="1" style="106" min="16" max="16"/>
+    <col width="10.5" customWidth="1" style="106" min="17" max="17"/>
+    <col width="10.5" customWidth="1" style="106" min="18" max="18"/>
+    <col width="10.5" customWidth="1" style="106" min="19" max="19"/>
+    <col width="10.5" customWidth="1" style="106" min="20" max="20"/>
+    <col width="10.5" customWidth="1" style="106" min="21" max="21"/>
+    <col width="10.5" customWidth="1" style="106" min="22" max="22"/>
+    <col width="10.5" customWidth="1" style="106" min="23" max="23"/>
+    <col width="10.5" customWidth="1" style="106" min="24" max="24"/>
+    <col width="10.5" customWidth="1" style="106" min="25" max="25"/>
+    <col width="10.5" customWidth="1" style="106" min="26" max="26"/>
+    <col width="10.5" customWidth="1" style="106" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" s="106">
+      <c r="A1" s="116" t="inlineStr">
+        <is>
+          <t>士林</t>
+        </is>
+      </c>
+      <c r="B1" s="117" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C1" s="117" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="D1" s="117" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="E1" s="117" t="inlineStr">
+        <is>
+          <t>CPU
+零搭售</t>
+        </is>
+      </c>
+      <c r="F1" s="118" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="G1" s="119" t="inlineStr">
+        <is>
+          <t>iPhone</t>
+        </is>
+      </c>
+      <c r="H1" s="119" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="I1" s="119" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="J1" s="119" t="inlineStr">
+        <is>
+          <t>iPhone
+零搭售</t>
+        </is>
+      </c>
+      <c r="K1" s="120" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="L1" s="121" t="inlineStr">
+        <is>
+          <t>iPad</t>
+        </is>
+      </c>
+      <c r="M1" s="121" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="N1" s="121" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="O1" s="121" t="inlineStr">
+        <is>
+          <t>iPad
+零搭售</t>
+        </is>
+      </c>
+      <c r="P1" s="122" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="Q1" s="123" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="R1" s="123" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="S1" s="123" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="T1" s="123" t="inlineStr">
+        <is>
+          <t>Watch
+零搭售</t>
+        </is>
+      </c>
+      <c r="U1" s="124" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="V1" s="125" t="inlineStr">
+        <is>
+          <t>AirPods</t>
+        </is>
+      </c>
+      <c r="W1" s="125" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="X1" s="125" t="inlineStr">
+        <is>
+          <t>搭售率</t>
+        </is>
+      </c>
+      <c r="Y1" s="125" t="inlineStr">
+        <is>
+          <t>AirPods
+零搭售</t>
+        </is>
+      </c>
+      <c r="Z1" s="126" t="inlineStr">
+        <is>
+          <t>零搭售
+比例</t>
+        </is>
+      </c>
+      <c r="AA1" s="127" t="inlineStr">
+        <is>
+          <t>3PP
+搭售率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1" s="106">
+      <c r="A2" s="128" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="B2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="130" t="n"/>
+      <c r="E2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="131" t="n"/>
+      <c r="G2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="130" t="n"/>
+      <c r="J2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="131" t="n"/>
+      <c r="L2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="130" t="n"/>
+      <c r="O2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="131" t="n"/>
+      <c r="Q2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="130" t="n"/>
+      <c r="T2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="131" t="n"/>
+      <c r="V2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="130" t="n"/>
+      <c r="Y2" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="131" t="n"/>
+      <c r="AA2" s="132" t="n"/>
+    </row>
+    <row r="3" ht="38" customHeight="1" s="106">
+      <c r="A3" s="128" t="inlineStr">
+        <is>
+          <t>Dean</t>
+        </is>
+      </c>
+      <c r="B3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="140" t="n"/>
+      <c r="E3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="155" t="n"/>
+      <c r="G3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="133" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="133" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="133" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" s="134" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O3" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" s="133" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" s="134" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA3" s="136" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1" s="106">
+      <c r="A4" s="128" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="130" t="n"/>
+      <c r="E4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="131" t="n"/>
+      <c r="G4" s="129" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="129" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" s="137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="130" t="n"/>
+      <c r="O4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="131" t="n"/>
+      <c r="Q4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="130" t="n"/>
+      <c r="T4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="131" t="n"/>
+      <c r="V4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="130" t="n"/>
+      <c r="Y4" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="131" t="n"/>
+      <c r="AA4" s="139" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1" s="106">
+      <c r="A5" s="128" t="inlineStr">
+        <is>
+          <t>Nana</t>
+        </is>
+      </c>
+      <c r="B5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="133" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="134" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="133" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" s="134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="140" t="n"/>
+      <c r="T5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" s="135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="133" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="135" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AA5" s="136" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1" s="106">
+      <c r="A6" s="128" t="inlineStr">
+        <is>
+          <t>Zoe</t>
+        </is>
+      </c>
+      <c r="B6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="130" t="n"/>
+      <c r="E6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="131" t="n"/>
+      <c r="G6" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="129" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="138" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="129" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="137" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V6" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="137" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="129" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="138" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AA6" s="139" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1" s="106">
+      <c r="A7" s="128" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+      <c r="B7" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="133" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="134" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="133" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="140" t="n"/>
+      <c r="T7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="155" t="n"/>
+      <c r="V7" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="133" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="136" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1" s="106">
+      <c r="A8" s="128" t="inlineStr">
+        <is>
+          <t>Tanya</t>
+        </is>
+      </c>
+      <c r="B8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="130" t="n"/>
+      <c r="E8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="131" t="n"/>
+      <c r="G8" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="129" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" s="137" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J8" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="138" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L8" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="129" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="130" t="n"/>
+      <c r="Y8" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="139" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1" s="106">
+      <c r="A9" s="141" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="142" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="142" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="142" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" s="142" t="n">
+        <v>62</v>
+      </c>
+      <c r="I9" s="143" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J9" s="142" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="144" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L9" s="142" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" s="142" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" s="143" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O9" s="142" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="144" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q9" s="142" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" s="142" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" s="143" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T9" s="142" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" s="144" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V9" s="142" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" s="142" t="n">
+        <v>7</v>
+      </c>
+      <c r="X9" s="143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y9" s="142" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" s="144" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA9" s="145" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1" s="106">
+      <c r="A10" s="146" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B10" s="147" t="n">
+        <v>23</v>
+      </c>
+      <c r="C10" s="147" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="148" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E10" s="147" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="149" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G10" s="147" t="n">
+        <v>81</v>
+      </c>
+      <c r="H10" s="147" t="n">
+        <v>295</v>
+      </c>
+      <c r="I10" s="148" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J10" s="147" t="n">
+        <v>45</v>
+      </c>
+      <c r="K10" s="149" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L10" s="147" t="n">
+        <v>51</v>
+      </c>
+      <c r="M10" s="147" t="n">
+        <v>122</v>
+      </c>
+      <c r="N10" s="148" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O10" s="147" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" s="149" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q10" s="147" t="n">
+        <v>37</v>
+      </c>
+      <c r="R10" s="147" t="n">
+        <v>63</v>
+      </c>
+      <c r="S10" s="148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T10" s="147" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" s="149" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V10" s="147" t="n">
+        <v>45</v>
+      </c>
+      <c r="W10" s="147" t="n">
+        <v>86</v>
+      </c>
+      <c r="X10" s="148" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y10" s="147" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z10" s="149" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AA10" s="150" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1" s="106">
+      <c r="A11" s="146" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B11" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="151" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" s="152" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E11" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="151" t="n">
+        <v>62</v>
+      </c>
+      <c r="H11" s="151" t="n">
+        <v>220</v>
+      </c>
+      <c r="I11" s="152" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J11" s="151" t="n">
+        <v>43</v>
+      </c>
+      <c r="K11" s="153" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L11" s="151" t="n">
+        <v>56</v>
+      </c>
+      <c r="M11" s="151" t="n">
+        <v>156</v>
+      </c>
+      <c r="N11" s="152" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O11" s="151" t="n">
+        <v>12</v>
+      </c>
+      <c r="P11" s="153" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q11" s="151" t="n">
+        <v>30</v>
+      </c>
+      <c r="R11" s="151" t="n">
+        <v>51</v>
+      </c>
+      <c r="S11" s="152" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T11" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="U11" s="153" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V11" s="151" t="n">
+        <v>37</v>
+      </c>
+      <c r="W11" s="151" t="n">
+        <v>74</v>
+      </c>
+      <c r="X11" s="152" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z11" s="153" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AA11" s="154" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1" s="106">
+      <c r="A12" s="146" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B12" s="147" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="147" t="n">
+        <v>36</v>
+      </c>
+      <c r="D12" s="148" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="147" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="149" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G12" s="147" t="n">
+        <v>79</v>
+      </c>
+      <c r="H12" s="147" t="n">
+        <v>243</v>
+      </c>
+      <c r="I12" s="148" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J12" s="147" t="n">
+        <v>56</v>
+      </c>
+      <c r="K12" s="149" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L12" s="147" t="n">
+        <v>32</v>
+      </c>
+      <c r="M12" s="147" t="n">
+        <v>87</v>
+      </c>
+      <c r="N12" s="148" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O12" s="147" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" s="149" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Q12" s="147" t="n">
+        <v>29</v>
+      </c>
+      <c r="R12" s="147" t="n">
+        <v>45</v>
+      </c>
+      <c r="S12" s="148" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T12" s="147" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" s="149" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V12" s="147" t="n">
+        <v>48</v>
+      </c>
+      <c r="W12" s="147" t="n">
+        <v>89</v>
+      </c>
+      <c r="X12" s="148" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y12" s="147" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z12" s="149" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AA12" s="150" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4251,7 +4664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4594,7 +5007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4937,7 +5350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5107,7 +5520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5729,7 +6142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7000,6 +7413,569 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.83203125" customWidth="1" style="106" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="23" customHeight="1" s="106">
+      <c r="A1" s="177" t="inlineStr">
+        <is>
+          <t>總銷售台數</t>
+        </is>
+      </c>
+      <c r="B1" s="177" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C1" s="177" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D1" s="177" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E1" s="177" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F1" s="177" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G1" s="177" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H1" s="177" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="I1" s="177" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="J1" s="177" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="K1" s="177" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="L1" s="177" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="M1" s="177" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="N1" s="177" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="O1" s="177" t="inlineStr">
+        <is>
+          <t>總計</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="23" customHeight="1" s="106">
+      <c r="A2" s="179" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B2" s="170" t="n"/>
+      <c r="C2" s="170" t="n"/>
+      <c r="D2" s="170" t="n"/>
+      <c r="E2" s="170" t="n"/>
+      <c r="F2" s="170" t="n"/>
+      <c r="G2" s="170" t="n"/>
+      <c r="H2" s="170" t="n"/>
+      <c r="I2" s="170" t="n"/>
+      <c r="J2" s="170" t="n"/>
+      <c r="K2" s="170" t="n"/>
+      <c r="L2" s="170" t="n"/>
+      <c r="M2" s="170" t="n"/>
+      <c r="N2" s="170" t="n"/>
+      <c r="O2" s="170" t="n"/>
+    </row>
+    <row r="3" ht="23" customHeight="1" s="106">
+      <c r="A3" s="179" t="inlineStr">
+        <is>
+          <t>iPad</t>
+        </is>
+      </c>
+      <c r="B3" s="170" t="n"/>
+      <c r="C3" s="170" t="n"/>
+      <c r="D3" s="170" t="n"/>
+      <c r="E3" s="170" t="n"/>
+      <c r="F3" s="170" t="n"/>
+      <c r="G3" s="170" t="n"/>
+      <c r="H3" s="170" t="n"/>
+      <c r="I3" s="170" t="n"/>
+      <c r="J3" s="170" t="n"/>
+      <c r="K3" s="170" t="n"/>
+      <c r="L3" s="170" t="n"/>
+      <c r="M3" s="170" t="n"/>
+      <c r="N3" s="170" t="n"/>
+      <c r="O3" s="170" t="n"/>
+    </row>
+    <row r="4" ht="23" customHeight="1" s="106">
+      <c r="A4" s="179" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="B4" s="170" t="n"/>
+      <c r="C4" s="170" t="n"/>
+      <c r="D4" s="170" t="n"/>
+      <c r="E4" s="170" t="n"/>
+      <c r="F4" s="170" t="n"/>
+      <c r="G4" s="170" t="n"/>
+      <c r="H4" s="170" t="n"/>
+      <c r="I4" s="170" t="n"/>
+      <c r="J4" s="170" t="n"/>
+      <c r="K4" s="170" t="n"/>
+      <c r="L4" s="170" t="n"/>
+      <c r="M4" s="170" t="n"/>
+      <c r="N4" s="170" t="n"/>
+      <c r="O4" s="170" t="n"/>
+    </row>
+    <row r="5" ht="23" customHeight="1" s="106">
+      <c r="A5" s="179" t="inlineStr">
+        <is>
+          <t>Pencil</t>
+        </is>
+      </c>
+      <c r="B5" s="170" t="n"/>
+      <c r="C5" s="170" t="n"/>
+      <c r="D5" s="170" t="n"/>
+      <c r="E5" s="170" t="n"/>
+      <c r="F5" s="170" t="n"/>
+      <c r="G5" s="170" t="n"/>
+      <c r="H5" s="170" t="n"/>
+      <c r="I5" s="170" t="n"/>
+      <c r="J5" s="170" t="n"/>
+      <c r="K5" s="170" t="n"/>
+      <c r="L5" s="170" t="n"/>
+      <c r="M5" s="170" t="n"/>
+      <c r="N5" s="170" t="n"/>
+      <c r="O5" s="170" t="n"/>
+    </row>
+    <row r="6" ht="23" customHeight="1" s="106">
+      <c r="A6" s="179" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="B6" s="170" t="n"/>
+      <c r="C6" s="170" t="n"/>
+      <c r="D6" s="170" t="n"/>
+      <c r="E6" s="170" t="n"/>
+      <c r="F6" s="170" t="n"/>
+      <c r="G6" s="170" t="n"/>
+      <c r="H6" s="170" t="n"/>
+      <c r="I6" s="170" t="n"/>
+      <c r="J6" s="170" t="n"/>
+      <c r="K6" s="170" t="n"/>
+      <c r="L6" s="170" t="n"/>
+      <c r="M6" s="170" t="n"/>
+      <c r="N6" s="170" t="n"/>
+      <c r="O6" s="170" t="n"/>
+    </row>
+    <row r="7" ht="23" customHeight="1" s="106">
+      <c r="A7" s="177" t="inlineStr">
+        <is>
+          <t>教育價台數</t>
+        </is>
+      </c>
+      <c r="B7" s="177" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C7" s="177" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D7" s="177" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E7" s="177" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F7" s="177" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G7" s="177" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H7" s="177" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="I7" s="177" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="J7" s="177" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="K7" s="177" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="L7" s="177" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="M7" s="177" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="N7" s="177" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="O7" s="177" t="inlineStr">
+        <is>
+          <t>總計</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23" customHeight="1" s="106">
+      <c r="A8" s="179" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B8" s="170" t="n"/>
+      <c r="C8" s="170" t="n"/>
+      <c r="D8" s="170" t="n"/>
+      <c r="E8" s="170" t="n"/>
+      <c r="F8" s="170" t="n"/>
+      <c r="G8" s="170" t="n"/>
+      <c r="H8" s="170" t="n"/>
+      <c r="I8" s="170" t="n"/>
+      <c r="J8" s="170" t="n"/>
+      <c r="K8" s="170" t="n"/>
+      <c r="L8" s="170" t="n"/>
+      <c r="M8" s="170" t="n"/>
+      <c r="N8" s="170" t="n"/>
+      <c r="O8" s="170" t="n"/>
+    </row>
+    <row r="9" ht="23" customHeight="1" s="106">
+      <c r="A9" s="179" t="inlineStr">
+        <is>
+          <t>iPad</t>
+        </is>
+      </c>
+      <c r="B9" s="170" t="n"/>
+      <c r="C9" s="170" t="n"/>
+      <c r="D9" s="170" t="n"/>
+      <c r="E9" s="170" t="n"/>
+      <c r="F9" s="170" t="n"/>
+      <c r="G9" s="170" t="n"/>
+      <c r="H9" s="170" t="n"/>
+      <c r="I9" s="170" t="n"/>
+      <c r="J9" s="170" t="n"/>
+      <c r="K9" s="170" t="n"/>
+      <c r="L9" s="170" t="n"/>
+      <c r="M9" s="170" t="n"/>
+      <c r="N9" s="170" t="n"/>
+      <c r="O9" s="170" t="n"/>
+    </row>
+    <row r="10" ht="23" customHeight="1" s="106">
+      <c r="A10" s="179" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="B10" s="170" t="n"/>
+      <c r="C10" s="170" t="n"/>
+      <c r="D10" s="170" t="n"/>
+      <c r="E10" s="170" t="n"/>
+      <c r="F10" s="170" t="n"/>
+      <c r="G10" s="170" t="n"/>
+      <c r="H10" s="170" t="n"/>
+      <c r="I10" s="170" t="n"/>
+      <c r="J10" s="170" t="n"/>
+      <c r="K10" s="170" t="n"/>
+      <c r="L10" s="170" t="n"/>
+      <c r="M10" s="170" t="n"/>
+      <c r="N10" s="170" t="n"/>
+      <c r="O10" s="170" t="n"/>
+    </row>
+    <row r="11" ht="23" customHeight="1" s="106">
+      <c r="A11" s="179" t="inlineStr">
+        <is>
+          <t>Pencil</t>
+        </is>
+      </c>
+      <c r="B11" s="170" t="n"/>
+      <c r="C11" s="170" t="n"/>
+      <c r="D11" s="170" t="n"/>
+      <c r="E11" s="170" t="n"/>
+      <c r="F11" s="170" t="n"/>
+      <c r="G11" s="170" t="n"/>
+      <c r="H11" s="170" t="n"/>
+      <c r="I11" s="170" t="n"/>
+      <c r="J11" s="170" t="n"/>
+      <c r="K11" s="170" t="n"/>
+      <c r="L11" s="170" t="n"/>
+      <c r="M11" s="170" t="n"/>
+      <c r="N11" s="170" t="n"/>
+      <c r="O11" s="170" t="n"/>
+    </row>
+    <row r="12" ht="23" customHeight="1" s="106">
+      <c r="A12" s="179" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="B12" s="170" t="n"/>
+      <c r="C12" s="170" t="n"/>
+      <c r="D12" s="170" t="n"/>
+      <c r="E12" s="170" t="n"/>
+      <c r="F12" s="170" t="n"/>
+      <c r="G12" s="170" t="n"/>
+      <c r="H12" s="170" t="n"/>
+      <c r="I12" s="170" t="n"/>
+      <c r="J12" s="170" t="n"/>
+      <c r="K12" s="170" t="n"/>
+      <c r="L12" s="170" t="n"/>
+      <c r="M12" s="170" t="n"/>
+      <c r="N12" s="170" t="n"/>
+      <c r="O12" s="170" t="n"/>
+    </row>
+    <row r="13" ht="23" customHeight="1" s="106">
+      <c r="A13" s="177" t="inlineStr">
+        <is>
+          <t>教育價佔比</t>
+        </is>
+      </c>
+      <c r="B13" s="177" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C13" s="177" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D13" s="177" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E13" s="177" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F13" s="177" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G13" s="177" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H13" s="177" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="I13" s="177" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="J13" s="177" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="K13" s="177" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="L13" s="177" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="M13" s="177" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="N13" s="177" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="O13" s="177" t="inlineStr">
+        <is>
+          <t>總計</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1" s="106">
+      <c r="A14" s="179" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B14" s="175" t="n"/>
+      <c r="C14" s="175" t="n"/>
+      <c r="D14" s="175" t="n"/>
+      <c r="E14" s="175" t="n"/>
+      <c r="F14" s="175" t="n"/>
+      <c r="G14" s="175" t="n"/>
+      <c r="H14" s="175" t="n"/>
+      <c r="I14" s="175" t="n"/>
+      <c r="J14" s="175" t="n"/>
+      <c r="K14" s="175" t="n"/>
+      <c r="L14" s="175" t="n"/>
+      <c r="M14" s="175" t="n"/>
+      <c r="N14" s="175" t="n"/>
+      <c r="O14" s="175" t="n"/>
+    </row>
+    <row r="15" ht="23" customHeight="1" s="106">
+      <c r="A15" s="179" t="inlineStr">
+        <is>
+          <t>iPad</t>
+        </is>
+      </c>
+      <c r="B15" s="175" t="n"/>
+      <c r="C15" s="175" t="n"/>
+      <c r="D15" s="175" t="n"/>
+      <c r="E15" s="175" t="n"/>
+      <c r="F15" s="175" t="n"/>
+      <c r="G15" s="175" t="n"/>
+      <c r="H15" s="175" t="n"/>
+      <c r="I15" s="175" t="n"/>
+      <c r="J15" s="175" t="n"/>
+      <c r="K15" s="175" t="n"/>
+      <c r="L15" s="175" t="n"/>
+      <c r="M15" s="175" t="n"/>
+      <c r="N15" s="175" t="n"/>
+      <c r="O15" s="175" t="n"/>
+    </row>
+    <row r="16" ht="23" customHeight="1" s="106">
+      <c r="A16" s="179" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="B16" s="175" t="n"/>
+      <c r="C16" s="175" t="n"/>
+      <c r="D16" s="175" t="n"/>
+      <c r="E16" s="175" t="n"/>
+      <c r="F16" s="175" t="n"/>
+      <c r="G16" s="175" t="n"/>
+      <c r="H16" s="175" t="n"/>
+      <c r="I16" s="175" t="n"/>
+      <c r="J16" s="175" t="n"/>
+      <c r="K16" s="175" t="n"/>
+      <c r="L16" s="175" t="n"/>
+      <c r="M16" s="175" t="n"/>
+      <c r="N16" s="175" t="n"/>
+      <c r="O16" s="175" t="n"/>
+    </row>
+    <row r="17" ht="23" customHeight="1" s="106">
+      <c r="A17" s="179" t="inlineStr">
+        <is>
+          <t>Pencil</t>
+        </is>
+      </c>
+      <c r="B17" s="175" t="n"/>
+      <c r="C17" s="175" t="n"/>
+      <c r="D17" s="175" t="n"/>
+      <c r="E17" s="175" t="n"/>
+      <c r="F17" s="175" t="n"/>
+      <c r="G17" s="175" t="n"/>
+      <c r="H17" s="175" t="n"/>
+      <c r="I17" s="175" t="n"/>
+      <c r="J17" s="175" t="n"/>
+      <c r="K17" s="175" t="n"/>
+      <c r="L17" s="175" t="n"/>
+      <c r="M17" s="175" t="n"/>
+      <c r="N17" s="175" t="n"/>
+      <c r="O17" s="175" t="n"/>
+    </row>
+    <row r="18" ht="23" customHeight="1" s="106">
+      <c r="A18" s="179" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="B18" s="175" t="n"/>
+      <c r="C18" s="175" t="n"/>
+      <c r="D18" s="175" t="n"/>
+      <c r="E18" s="175" t="n"/>
+      <c r="F18" s="175" t="n"/>
+      <c r="G18" s="175" t="n"/>
+      <c r="H18" s="175" t="n"/>
+      <c r="I18" s="175" t="n"/>
+      <c r="J18" s="175" t="n"/>
+      <c r="K18" s="175" t="n"/>
+      <c r="L18" s="175" t="n"/>
+      <c r="M18" s="175" t="n"/>
+      <c r="N18" s="175" t="n"/>
+      <c r="O18" s="175" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7081,7 +8057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7216,7 +8192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7541,7 +8517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8930,7 +9906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9453,7 +10429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9855,408 +10831,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col width="18.33203125" customWidth="1" style="106" min="2" max="2"/>
-    <col width="93" customWidth="1" style="106" min="3" max="3"/>
-    <col width="19.6640625" customWidth="1" style="106" min="5" max="5"/>
-    <col width="92.33203125" customWidth="1" style="106" min="6" max="6"/>
-    <col width="19" bestFit="1" customWidth="1" style="106" min="7" max="7"/>
-    <col width="19.1640625" customWidth="1" style="106" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1" s="106">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>排名</t>
-        </is>
-      </c>
-      <c r="B1" s="38" t="inlineStr">
-        <is>
-          <t>存貨代碼</t>
-        </is>
-      </c>
-      <c r="C1" s="38" t="inlineStr">
-        <is>
-          <t>品名</t>
-        </is>
-      </c>
-      <c r="D1" s="38" t="inlineStr">
-        <is>
-          <t>週銷累計 數量</t>
-        </is>
-      </c>
-      <c r="E1" s="38" t="inlineStr">
-        <is>
-          <t>存貨代碼</t>
-        </is>
-      </c>
-      <c r="F1" s="38" t="inlineStr">
-        <is>
-          <t>品名</t>
-        </is>
-      </c>
-      <c r="G1" s="38" t="inlineStr">
-        <is>
-          <t>月銷累計 數量</t>
-        </is>
-      </c>
-      <c r="H1" s="38" t="inlineStr">
-        <is>
-          <t>金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="49" customHeight="1" s="106">
-      <c r="A2" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="inlineStr">
-        <is>
-          <t>5902002</t>
-        </is>
-      </c>
-      <c r="C2" s="40" t="inlineStr">
-        <is>
-          <t>pqi iPhone 17 Pro 康寧鋼化玻璃保護貼 2.5D</t>
-        </is>
-      </c>
-      <c r="D2" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="40" t="inlineStr">
-        <is>
-          <t>5902002</t>
-        </is>
-      </c>
-      <c r="F2" s="40" t="inlineStr">
-        <is>
-          <t>pqi iPhone 17 Pro 康寧鋼化玻璃保護貼 2.5D</t>
-        </is>
-      </c>
-      <c r="G2" s="113" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" s="114" t="n">
-        <v>6490</v>
-      </c>
-    </row>
-    <row r="3" ht="49" customHeight="1" s="106">
-      <c r="A3" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="40" t="inlineStr">
-        <is>
-          <t>5901984</t>
-        </is>
-      </c>
-      <c r="C3" s="40" t="inlineStr">
-        <is>
-          <t>pqi-45W GaN氮化镓(2C)充電器MC32-白色</t>
-        </is>
-      </c>
-      <c r="D3" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="40" t="inlineStr">
-        <is>
-          <t>22400301</t>
-        </is>
-      </c>
-      <c r="F3" s="40" t="inlineStr">
-        <is>
-          <t>維修專用-裸裝滿版玻璃保貼iPhone 14 Pro Max</t>
-        </is>
-      </c>
-      <c r="G3" s="113" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="114" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="4" ht="49" customHeight="1" s="106">
-      <c r="A4" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>5901995</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="inlineStr">
-        <is>
-          <t>pqi AirPods Pro 3 皮革保護殼 - 黑色</t>
-        </is>
-      </c>
-      <c r="D4" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="40" t="inlineStr">
-        <is>
-          <t>46200219</t>
-        </is>
-      </c>
-      <c r="F4" s="40" t="inlineStr">
-        <is>
-          <t>pqi iPad (A16) 11吋 玻璃保護貼</t>
-        </is>
-      </c>
-      <c r="G4" s="113" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="114" t="n">
-        <v>2304</v>
-      </c>
-    </row>
-    <row r="5" ht="49" customHeight="1" s="106">
-      <c r="A5" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>5902003</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>pqi iPhone 17 Pro Max 康寧鋼化玻璃保護貼 2.5D</t>
-        </is>
-      </c>
-      <c r="D5" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="40" t="inlineStr">
-        <is>
-          <t>46200232</t>
-        </is>
-      </c>
-      <c r="F5" s="40" t="inlineStr">
-        <is>
-          <t>pqi iPhone 17 Pro / Pro Max 鏡頭貼 深藍</t>
-        </is>
-      </c>
-      <c r="G5" s="113" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="114" t="n">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="6" ht="49" customHeight="1" s="106">
-      <c r="A6" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>22400301</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>維修專用-裸裝滿版玻璃保貼iPhone 14 Pro Max</t>
-        </is>
-      </c>
-      <c r="D6" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="40" t="inlineStr">
-        <is>
-          <t>5901984</t>
-        </is>
-      </c>
-      <c r="F6" s="40" t="inlineStr">
-        <is>
-          <t>pqi-45W GaN氮化镓(2C)充電器MC32-白色</t>
-        </is>
-      </c>
-      <c r="G6" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="114" t="n">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="7" ht="49" customHeight="1" s="106">
-      <c r="A7" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>46200123</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>VAP-iPad mini 8.3吋 (6/A17 Pro) 玻璃保護貼</t>
-        </is>
-      </c>
-      <c r="D7" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="40" t="inlineStr">
-        <is>
-          <t>5901995</t>
-        </is>
-      </c>
-      <c r="F7" s="40" t="inlineStr">
-        <is>
-          <t>pqi AirPods Pro 3 皮革保護殼 - 黑色</t>
-        </is>
-      </c>
-      <c r="G7" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="114" t="n">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="8" ht="49" customHeight="1" s="106">
-      <c r="A8" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>46200168</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>VAP-MacBook Pro 14吋亮面保護貼</t>
-        </is>
-      </c>
-      <c r="D8" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="40" t="inlineStr">
-        <is>
-          <t>5902003</t>
-        </is>
-      </c>
-      <c r="F8" s="40" t="inlineStr">
-        <is>
-          <t>pqi iPhone 17 Pro Max 康寧鋼化玻璃保護貼 2.5D</t>
-        </is>
-      </c>
-      <c r="G8" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="114" t="n">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="9" ht="49" customHeight="1" s="106">
-      <c r="A9" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>46200211</t>
-        </is>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>@VAP iPhone 16e 玻璃保護貼</t>
-        </is>
-      </c>
-      <c r="D9" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="40" t="inlineStr">
-        <is>
-          <t>46200123</t>
-        </is>
-      </c>
-      <c r="F9" s="40" t="inlineStr">
-        <is>
-          <t>VAP-iPad mini 8.3吋 (6/A17 Pro) 玻璃保護貼</t>
-        </is>
-      </c>
-      <c r="G9" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="114" t="n">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="10" ht="49" customHeight="1" s="106">
-      <c r="A10" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>46200217</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>@pqi-iPad Air 11吋 (M3/M4)-玻璃保護貼</t>
-        </is>
-      </c>
-      <c r="D10" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="40" t="inlineStr">
-        <is>
-          <t>46200168</t>
-        </is>
-      </c>
-      <c r="F10" s="40" t="inlineStr">
-        <is>
-          <t>VAP-MacBook Pro 14吋亮面保護貼</t>
-        </is>
-      </c>
-      <c r="G10" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="114" t="n">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="11" ht="49" customHeight="1" s="106">
-      <c r="A11" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>46200229</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>pqi iPhone 17 Pro / Pro Max 鏡頭貼 銀</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="40" t="inlineStr">
-        <is>
-          <t>46200211</t>
-        </is>
-      </c>
-      <c r="F11" s="40" t="inlineStr">
-        <is>
-          <t>@VAP iPhone 16e 玻璃保護貼</t>
-        </is>
-      </c>
-      <c r="G11" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="114" t="n">
-        <v>981</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/週報模板.xlsx
+++ b/週報模板.xlsx
@@ -38,7 +38,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <name val="新細明體"/>
       <charset val="136"/>
@@ -236,6 +236,17 @@
     <font>
       <name val="新細明體"/>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <color theme="0"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <b val="1"/>
+      <color theme="0"/>
       <sz val="14"/>
     </font>
   </fonts>
@@ -739,7 +750,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1264,6 +1275,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8007,8 +8033,8 @@
     <row r="2" ht="26" customHeight="1" s="106">
       <c r="A2" s="158" t="n"/>
       <c r="B2" s="158" t="n"/>
-      <c r="C2" s="159" t="n"/>
-      <c r="D2" s="159" t="n"/>
+      <c r="C2" s="180" t="n"/>
+      <c r="D2" s="180" t="n"/>
     </row>
     <row r="3" ht="26" customHeight="1" s="106">
       <c r="A3" s="158" t="n"/>
@@ -8104,10 +8130,10 @@
     <row r="2" ht="22" customHeight="1" s="106">
       <c r="A2" s="163" t="n"/>
       <c r="B2" s="163" t="n"/>
-      <c r="C2" s="159" t="n"/>
-      <c r="D2" s="159" t="n"/>
-      <c r="E2" s="159" t="n"/>
-      <c r="F2" s="159" t="n"/>
+      <c r="C2" s="180" t="n"/>
+      <c r="D2" s="180" t="n"/>
+      <c r="E2" s="180" t="n"/>
+      <c r="F2" s="180" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1" s="106">
       <c r="A3" s="163" t="n"/>
@@ -8155,10 +8181,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="164" t="n"/>
-      <c r="D8" s="164" t="n"/>
-      <c r="E8" s="164" t="n"/>
-      <c r="F8" s="164" t="n"/>
+      <c r="C8" s="160" t="n"/>
+      <c r="D8" s="160" t="n"/>
+      <c r="E8" s="160" t="n"/>
+      <c r="F8" s="160" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1" s="106">
       <c r="A9" s="159" t="n"/>
@@ -8206,42 +8232,42 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="106">
       <c r="A1" s="170" t="n"/>
-      <c r="B1" s="171" t="inlineStr">
+      <c r="B1" s="181" t="inlineStr">
         <is>
           <t>SUN</t>
         </is>
       </c>
-      <c r="C1" s="171" t="inlineStr">
+      <c r="C1" s="181" t="inlineStr">
         <is>
           <t>MON</t>
         </is>
       </c>
-      <c r="D1" s="171" t="inlineStr">
+      <c r="D1" s="181" t="inlineStr">
         <is>
           <t>TUE</t>
         </is>
       </c>
-      <c r="E1" s="171" t="inlineStr">
+      <c r="E1" s="181" t="inlineStr">
         <is>
           <t>WED</t>
         </is>
       </c>
-      <c r="F1" s="171" t="inlineStr">
+      <c r="F1" s="181" t="inlineStr">
         <is>
           <t>THU</t>
         </is>
       </c>
-      <c r="G1" s="171" t="inlineStr">
+      <c r="G1" s="181" t="inlineStr">
         <is>
           <t>FRI</t>
         </is>
       </c>
-      <c r="H1" s="171" t="inlineStr">
+      <c r="H1" s="181" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="I1" s="171" t="inlineStr">
+      <c r="I1" s="181" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -8253,7 +8279,7 @@
       <c r="N1" s="170" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1" s="106">
-      <c r="A2" s="172" t="inlineStr">
+      <c r="A2" s="182" t="inlineStr">
         <is>
           <t>上週</t>
         </is>
@@ -8273,7 +8299,7 @@
       <c r="N2" s="170" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1" s="106">
-      <c r="A3" s="172" t="inlineStr">
+      <c r="A3" s="182" t="inlineStr">
         <is>
           <t>本週</t>
         </is>
@@ -8293,7 +8319,7 @@
       <c r="N3" s="170" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="106">
-      <c r="A4" s="172" t="inlineStr">
+      <c r="A4" s="182" t="inlineStr">
         <is>
           <t>WoW 差異人數</t>
         </is>
@@ -8313,7 +8339,7 @@
       <c r="N4" s="170" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="106">
-      <c r="A5" s="172" t="inlineStr">
+      <c r="A5" s="182" t="inlineStr">
         <is>
           <t>WoW 差異比例</t>
         </is>
@@ -8349,75 +8375,75 @@
       <c r="N6" s="170" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1" s="106">
-      <c r="A7" s="171" t="n"/>
-      <c r="B7" s="171" t="inlineStr">
+      <c r="A7" s="181" t="n"/>
+      <c r="B7" s="181" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="C7" s="171" t="inlineStr">
+      <c r="C7" s="181" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="D7" s="171" t="inlineStr">
+      <c r="D7" s="181" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="E7" s="171" t="inlineStr">
+      <c r="E7" s="181" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="F7" s="171" t="inlineStr">
+      <c r="F7" s="181" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="G7" s="171" t="inlineStr">
+      <c r="G7" s="181" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H7" s="171" t="inlineStr">
+      <c r="H7" s="181" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="I7" s="171" t="inlineStr">
+      <c r="I7" s="181" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="J7" s="171" t="inlineStr">
+      <c r="J7" s="181" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="K7" s="171" t="inlineStr">
+      <c r="K7" s="181" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="L7" s="171" t="inlineStr">
+      <c r="L7" s="181" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="M7" s="171" t="inlineStr">
+      <c r="M7" s="181" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="N7" s="171" t="inlineStr">
+      <c r="N7" s="181" t="inlineStr">
         <is>
           <t>總計</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="106">
-      <c r="A8" s="176" t="inlineStr">
+      <c r="A8" s="183" t="inlineStr">
         <is>
           <t>人流</t>
         </is>
@@ -8469,23 +8495,23 @@
       <c r="N10" s="170" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1" s="106">
-      <c r="A11" s="171" t="n"/>
-      <c r="B11" s="171" t="n"/>
-      <c r="C11" s="177" t="inlineStr">
+      <c r="A11" s="181" t="n"/>
+      <c r="B11" s="181" t="n"/>
+      <c r="C11" s="184" t="inlineStr">
         <is>
           <t>差異</t>
         </is>
       </c>
-      <c r="D11" s="171" t="n"/>
-      <c r="E11" s="171" t="n"/>
-      <c r="F11" s="177" t="inlineStr">
+      <c r="D11" s="181" t="n"/>
+      <c r="E11" s="181" t="n"/>
+      <c r="F11" s="184" t="inlineStr">
         <is>
           <t>差異</t>
         </is>
       </c>
-      <c r="G11" s="171" t="n"/>
-      <c r="H11" s="171" t="n"/>
-      <c r="I11" s="177" t="inlineStr">
+      <c r="G11" s="181" t="n"/>
+      <c r="H11" s="181" t="n"/>
+      <c r="I11" s="184" t="inlineStr">
         <is>
           <t>差異</t>
         </is>
